--- a/kinds_Listen_EPS.xlsx
+++ b/kinds_Listen_EPS.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mục lục" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKILL.md" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="310001" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="310002" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="310003" sheetId="5" state="visible" r:id="rId5"/>
@@ -534,6 +534,8 @@
           <t>Danh sách nội dung — Listen_EPS</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -718,6 +720,11 @@
           <t>Kind: 3410005</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -725,6 +732,11 @@
           <t>KIND 3410005 — Chọn câu nối tiếp EPS (Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -732,6 +744,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -835,6 +852,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -849,6 +871,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -892,6 +919,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -967,6 +999,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -1002,6 +1039,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -1051,6 +1093,11 @@
           <t>Phân biệt với 310004/3410004</t>
         </is>
       </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -1072,6 +1119,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -1182,6 +1234,11 @@
           <t>SKILL.md — Listen_EPS</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -1189,6 +1246,11 @@
           <t>EPS-TOPIK Listening Question Generator (Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -1203,6 +1265,11 @@
           <t>Khi nao dung skill nay</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -1231,6 +1298,11 @@
           <t>Cau truc thu muc</t>
         </is>
       </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -1350,6 +1422,11 @@
           <t>Output Format (JSON)</t>
         </is>
       </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -1763,6 +1840,11 @@
           <t>Danh muc chu de (topic)</t>
         </is>
       </c>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="10" t="n"/>
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="10" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="13" t="inlineStr">
@@ -2194,6 +2276,11 @@
           <t>Chien luoc bay dap an sai (distractor_trap)</t>
         </is>
       </c>
+      <c r="B114" s="10" t="n"/>
+      <c r="C114" s="10" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="13" t="inlineStr">
@@ -2572,6 +2659,11 @@
           <t>Dac diem cau hoi (question_feature)</t>
         </is>
       </c>
+      <c r="B142" s="10" t="n"/>
+      <c r="C142" s="10" t="n"/>
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="10" t="n"/>
+      <c r="F142" s="10" t="n"/>
     </row>
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="13" t="inlineStr">
@@ -2923,6 +3015,11 @@
           <t>Cau truc ngu phap trong audio (grammar_semantic)</t>
         </is>
       </c>
+      <c r="B167" s="10" t="n"/>
+      <c r="C167" s="10" t="n"/>
+      <c r="D167" s="10" t="n"/>
+      <c r="E167" s="10" t="n"/>
+      <c r="F167" s="10" t="n"/>
     </row>
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="13" t="inlineStr">
@@ -3319,6 +3416,11 @@
           <t>Cau truc audio (audio_format)</t>
         </is>
       </c>
+      <c r="B192" s="10" t="n"/>
+      <c r="C192" s="10" t="n"/>
+      <c r="D192" s="10" t="n"/>
+      <c r="E192" s="10" t="n"/>
+      <c r="F192" s="10" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="14" t="inlineStr">
@@ -3418,6 +3520,11 @@
           <t>Thang do kho (Difficulty Scale) — EPS kinds only</t>
         </is>
       </c>
+      <c r="B200" s="10" t="n"/>
+      <c r="C200" s="10" t="n"/>
+      <c r="D200" s="10" t="n"/>
+      <c r="E200" s="10" t="n"/>
+      <c r="F200" s="10" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="14" t="inlineStr">
@@ -3701,6 +3808,11 @@
           <t>Cap do giao tiep trong audio (speech_level)</t>
         </is>
       </c>
+      <c r="B221" s="10" t="n"/>
+      <c r="C221" s="10" t="n"/>
+      <c r="D221" s="10" t="n"/>
+      <c r="E221" s="10" t="n"/>
+      <c r="F221" s="10" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="14" t="inlineStr">
@@ -3756,6 +3868,11 @@
           <t>Quy tac chung khi gen cau hoi</t>
         </is>
       </c>
+      <c r="B227" s="10" t="n"/>
+      <c r="C227" s="10" t="n"/>
+      <c r="D227" s="10" t="n"/>
+      <c r="E227" s="10" t="n"/>
+      <c r="F227" s="10" t="n"/>
     </row>
     <row r="228" ht="22" customHeight="1">
       <c r="A228" s="13" t="inlineStr">
@@ -3945,6 +4062,11 @@
           <t>Workflow</t>
         </is>
       </c>
+      <c r="B254" s="10" t="n"/>
+      <c r="C254" s="10" t="n"/>
+      <c r="D254" s="10" t="n"/>
+      <c r="E254" s="10" t="n"/>
+      <c r="F254" s="10" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
@@ -4232,6 +4354,11 @@
           <t>Kind: 310001</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -4239,6 +4366,11 @@
           <t>KIND 310001 — Nhận diện từ/câu (EPS, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -4253,6 +4385,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -4356,6 +4493,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -4370,6 +4512,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -4413,6 +4560,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -4488,6 +4640,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -4516,6 +4673,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -4572,6 +4734,11 @@
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -4600,6 +4767,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -4704,6 +4876,11 @@
           <t>Kind: 310002</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -4711,6 +4888,11 @@
           <t>KIND 310002 — Nhìn hình chọn đáp án (EPS, Level 3) [ẢNH]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -4725,6 +4907,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -4840,6 +5027,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -4854,6 +5046,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -4897,6 +5094,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -4911,6 +5113,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -4960,6 +5167,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -5148,6 +5360,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -5162,6 +5379,11 @@
           <t>Quy tắc tạo audio và hình</t>
         </is>
       </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -5190,6 +5412,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -5337,6 +5564,11 @@
           <t>Kind: 310003</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -5344,6 +5576,11 @@
           <t>KIND 310003 — Chọn hình liên quan (EPS, Level 3) [ẢNH]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -5358,6 +5595,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -5473,6 +5715,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -5487,6 +5734,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -5530,6 +5782,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -5544,6 +5801,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -5565,6 +5827,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -5600,6 +5867,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -5614,6 +5886,11 @@
           <t>Quy tắc tạo 4 bức tranh</t>
         </is>
       </c>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -5649,6 +5926,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -5809,6 +6091,11 @@
           <t>Kind: 310004</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -5816,6 +6103,11 @@
           <t>KIND 310004 — Hỏi-đáp trực tiếp EPS (Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -5830,6 +6122,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -5933,6 +6230,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -5947,6 +6249,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -6002,6 +6309,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -6077,6 +6389,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -6105,6 +6422,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -6161,6 +6483,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -6253,6 +6580,11 @@
           <t>Kind: 310005</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -6260,6 +6592,11 @@
           <t>KIND 310005 — Trích xuất chi tiết (EPS, Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -6274,6 +6611,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -6377,6 +6719,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -6391,6 +6738,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -6446,6 +6798,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -6538,6 +6895,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -6580,6 +6942,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -6636,6 +7003,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -6722,6 +7094,11 @@
           <t>Kind: 310006</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -6729,6 +7106,11 @@
           <t>KIND 310006 — 2 câu hỏi EPS (Level 3)</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -6736,6 +7118,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -6839,6 +7226,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -6853,6 +7245,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -6908,6 +7305,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -6983,6 +7385,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -7060,6 +7467,11 @@
           <t>Cấu trúc đáp án — 2 câu hỏi con</t>
         </is>
       </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="13" t="inlineStr">
@@ -7137,6 +7549,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -7318,6 +7735,11 @@
           <t>Kind: 3410002</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -7325,6 +7747,11 @@
           <t>KIND 3410002 — Nhận diện giờ (EPS, Level 3) [ẢNH]</t>
         </is>
       </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
@@ -7332,6 +7759,11 @@
           <t>Thông tin cơ bản</t>
         </is>
       </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -7447,6 +7879,11 @@
           <t>Chủ đề thường gặp</t>
         </is>
       </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -7461,6 +7898,11 @@
           <t>Nhãn hệ thống</t>
         </is>
       </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -7504,6 +7946,11 @@
           <t>Chiến lược bẫy</t>
         </is>
       </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -7545,6 +7992,11 @@
           <t>Cấu trúc audio</t>
         </is>
       </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -7573,6 +8025,11 @@
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -7615,6 +8072,11 @@
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -7629,6 +8091,11 @@
           <t>Quy tắc tạo 4 đồng hồ</t>
         </is>
       </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -7685,6 +8152,11 @@
           <t>Ví dụ</t>
         </is>
       </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">

--- a/kinds_Listen_EPS.xlsx
+++ b/kinds_Listen_EPS.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -913,262 +913,274 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>answer_grammar</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>`ans_informal_polite`</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Chiến lược bẫy</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Bẫy</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>`trap_same_ending`</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Cả 4 phản hồi kết thúc cùng dạng</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>`trap_neg_없안`</t>
+          <t>`trap_same_ending`</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Phản hồi phủ định không phù hợp</t>
+          <t>Cả 4 phản hồi kết thúc cùng dạng</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>`trap_neg_없안`</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Phản hồi phủ định không phù hợp</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
           <t>`trap_shared_noun`</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Dùng lại từ trong câu phát biểu</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>• Một câu phát biểu, lời chào, hoặc tình huống giao tiếp (1-2 câu)</t>
-        </is>
-      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>• Ngữ cảnh: chào hỏi, cảm ơn, xin lỗi, yêu cầu, tạm biệt, giới thiệu</t>
+          <t>• Một câu phát biểu, lời chào, hoặc tình huống giao tiếp (1-2 câu)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>• Ví dụ: "안녕하세요. 처음 뵙겠습니다.", "잘 먹겠습니다.", "다녀오겠습니다."</t>
+          <t>• Ngữ cảnh: chào hỏi, cảm ơn, xin lỗi, yêu cầu, tạm biệt, giới thiệu</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
+          <t>• Ví dụ: "안녕하세요. 처음 뵙겠습니다.", "잘 먹겠습니다.", "다녀오겠습니다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
           <t>• Format: câu đơn, không có người nói</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>• 4 câu phản hồi có số thứ tự prefix</t>
-        </is>
-      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>• q_text: rỗng</t>
+          <t>• 4 câu phản hồi có số thứ tự prefix</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>• q_image: rỗng</t>
+          <t>• q_text: rỗng</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>• Format: ['1. 네, 반갑습니다.', '2. 네, 다녀오세요.', '3. 네, 안녕히 계세요.', '4. 네, 고맙습니다.']</t>
+          <t>• q_image: rỗng</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: phản hồi tự nhiên, phù hợp ngữ cảnh giao tiếp</t>
+          <t>• Format: ['1. 네, 반갑습니다.', '2. 네, 다녀오세요.', '3. 네, 안녕히 계세요.', '4. 네, 고맙습니다.']</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
+          <t>• Đáp án đúng: phản hồi tự nhiên, phù hợp ngữ cảnh giao tiếp</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
           <t>• Đáp án sai: câu đúng ngữ pháp nhưng sai ngữ cảnh (dùng cho tình huống khác)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Phân biệt với 310004/3410004</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>• 310004/3410004 (direct_match): câu hỏi WH rõ ràng, trả lời thông tin cụ thể</t>
-        </is>
-      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
+          <t>• 310004/3410004 (direct_match): câu hỏi WH rõ ràng, trả lời thông tin cụ thể</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
           <t>• 3410005 (pragmatic_response): câu phát biểu/lời chào, chọn phản hồi phù hợp về mặt giao tiếp</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>Audio: "안녕하세요. 처음 뵙겠습니다."</t>
-        </is>
-      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Đáp án: 1. 네, 반갑습니다.  2. 네, 다녀오세요.  3. 네, 안녕히 계세요.  4. 네, 고맙습니다.</t>
+          <t>Audio: "안녕하세요. 처음 뵙겠습니다."</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>Đúng: 1 (phản hồi phù hợp khi gặp lần đầu)</t>
+          <t>Đáp án: 1. 네, 반갑습니다.  2. 네, 다녀오세요.  3. 네, 안녕히 계세요.  4. 네, 고맙습니다.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>Audio: "잘 먹겠습니다."</t>
+          <t>Đúng: 1 (phản hồi phù hợp khi gặp lần đầu)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>Đáp án: 1. 많이 드세요.  2. 잘 가세요.  3. 감사합니다.  4. 안녕히 주무세요.</t>
+          <t>Audio: "잘 먹겠습니다."</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>Đúng: 1 (phản hồi phù hợp trước bữa ăn)</t>
+          <t>Đáp án: 1. 많이 드세요.  2. 잘 가세요.  3. 감사합니다.  4. 안녕히 주무세요.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Đúng: 1 (phản hồi phù hợp trước bữa ăn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Audio: "다녀오겠습니다."</t>
         </is>
@@ -1180,14 +1192,14 @@
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A29:F29"/>
@@ -1217,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F270"/>
+  <dimension ref="A1:F262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1255,14 +1267,14 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Skill tao cau hoi phan Nghe (듣기) cho ky thi EPS-TOPIK (Level 3 — danh cho nguoi lao dong nuoc ngoai tai Han Quoc) theo dung format JSON cua he thong Migii.</t>
+          <t>Skill tạo câu hỏi phần Nghe (듣기) cho kỳ thi EPS-TOPIK (Level 3 — dành cho người lao động nước ngoài tại Hàn Quốc) theo đúng format JSON của hệ thống Migii.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Khi nao dung skill nay</t>
+          <t>Khi nào dùng skill này</t>
         </is>
       </c>
       <c r="B5" s="10" t="n"/>
@@ -1274,28 +1286,28 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>• Khi user yeu cau tao/gen cau hoi nghe EPS-TOPIK</t>
+          <t>• Khi user yêu cầu tạo/gen câu hỏi nghe EPS-TOPIK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>• Khi user chi dinh kind cu the (vi du: "gen 310001", "tao cau hoi dang 3410005")</t>
+          <t>• Khi user chỉ định kind cụ thể (ví dụ: "gen 310001", "tạo câu hỏi dạng 3410005")</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>• Khi user yeu cau tao de thi nghe EPS</t>
+          <t>• Khi user yêu cầu tạo đề thi nghe EPS</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Cau truc thu muc</t>
+          <t>Cấu trúc thư mục</t>
         </is>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -1314,7 +1326,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>├── SKILL.md              ← File nay (overview + quy tac chung)</t>
+          <t>├── SKILL.md              ← File này (overview + quy tắc chung)</t>
         </is>
       </c>
     </row>
@@ -1328,84 +1340,84 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>│   └── save_listen.py    ← Script luu CSV/JSON theo kind</t>
+          <t>│   └── save_listen.py    ← Script lưu CSV/JSON theo kind</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>├── kinds/                ← Quy tac chi tiet tung dang</t>
+          <t>├── kinds/                ← Quy tắc chi tiết từng dạng</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>│   ├── 310001.md         Nhan dien tu/cau (EPS, gom 3410001)</t>
+          <t>│   ├── 310001.md         Nhận diện từ/câu (EPS, gồm 3410001)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>│   ├── 310002.md         Nhin hinh chon dap an (EPS, gom 3410003) [anh]</t>
+          <t>│   ├── 310002.md         Nhìn hình chọn đáp án (EPS, gồm 3410003) [ảnh]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>│   ├── 310003.md         Chon hinh lien quan (EPS, gom 3410006) [anh]</t>
+          <t>│   ├── 310003.md         Chọn hình liên quan (EPS, gồm 3410006) [ảnh]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>│   ├── 310004.md         Hoi-dap EPS (gom 3410004)</t>
+          <t>│   ├── 310004.md         Hỏi-đáp EPS (gồm 3410004)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>│   ├── 310005.md         Trich xuat chi tiet (EPS, gom 3410007)</t>
+          <t>│   ├── 310005.md         Trích xuất chi tiết (EPS, gồm 3410007)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>│   ├── 310006.md         2 cau hoi EPS</t>
+          <t>│   ├── 310006.md         2 câu hỏi EPS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>│   ├── 3410002.md        Nhan dien gio (EPS) [anh]</t>
+          <t>│   ├── 3410002.md        Nhận diện giờ (EPS) [ảnh]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>│   └── 3410005.md        Chon cau noi tiep EPS (pragmatic_response)</t>
+          <t>│   └── 3410005.md        Chọn câu nối tiếp EPS (pragmatic_response)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>└── samples.json          ← Mau cau hoi tham khao</t>
+          <t>└── samples.json          ← Mẫu câu hỏi tham khảo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Khi gen kind cu the, doc file kinds/{kind}.md tuong ung + file SKILL.md nay.</t>
+          <t>Khi gen kind cụ thể, đọc file kinds/{kind}.md tương ứng + file SKILL.md này.</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1443,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>Moi cau hoi PHAI tuan theo cau truc JSON sau:</t>
+          <t>Mỗi câu hỏi PHẢI tuân theo cấu trúc JSON sau:</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1457,7 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "title": "&lt;tieu de dang cau hoi bang tieng Han&gt;",</t>
+          <t xml:space="preserve">  "title": "&lt;tiêu đề dạng câu hỏi bằng tiếng Hàn&gt;",</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1485,7 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "g_text_audio": "&lt;noi dung audio / doan hoi thoai bang tieng Han&gt;",</t>
+          <t xml:space="preserve">    "g_text_audio": "&lt;nội dung audio / đoạn hội thoại bằng tiếng Hàn&gt;",</t>
         </is>
       </c>
     </row>
@@ -1487,14 +1499,14 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "vi": "&lt;ban dich tieng Viet&gt;",</t>
+          <t xml:space="preserve">      "vi": "&lt;bản dịch tiếng Việt&gt;",</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "en": "&lt;ban dich tieng Anh&gt;"</t>
+          <t xml:space="preserve">      "en": "&lt;bản dịch tiếng Anh&gt;"</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1555,7 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_text": "&lt;cau hoi phu neu co, neu khong thi de rong&gt;",</t>
+          <t xml:space="preserve">      "q_text": "&lt;câu hỏi phụ nếu có, nếu không thì để rỗng&gt;",</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1569,7 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_point": &lt;diem hoac null&gt;,</t>
+          <t xml:space="preserve">      "q_point": &lt;điểm hoặc null&gt;,</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1583,7 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "q_correct": &lt;so thu tu dap an dung 1-4&gt;,</t>
+          <t xml:space="preserve">      "q_correct": &lt;số thứ tự đáp án đúng 1-4&gt;,</t>
         </is>
       </c>
     </row>
@@ -1585,126 +1597,119 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "vi": "&lt;giai thich tieng Viet&gt;",</t>
+          <t xml:space="preserve">        "vi": "&lt;giải thích tiếng Việt — GHI RÕ trap type cho từng đáp án sai&gt;",</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "en": "&lt;giai thich tieng Anh&gt;"</t>
+          <t xml:space="preserve">        "en": "&lt;giải thích tiếng Anh&gt;"</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      },</t>
+          <t xml:space="preserve">      }</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "question_feature": "&lt;ma dac diem tu bang question_feature&gt;",</t>
+          <t xml:space="preserve">    }</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "difficulty": &lt;muc do kho 1-4&gt;,</t>
+          <t xml:space="preserve">  ],</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "distractor_traps": {</t>
+          <t xml:space="preserve">  "level": 3,</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "1": "&lt;trap code cho dap an 1 — rong neu la dap an dung&gt;",</t>
+          <t xml:space="preserve">  "kind": "&lt;mã kind&gt;",</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "2": "&lt;trap code cho dap an 2&gt;",</t>
+          <t xml:space="preserve">  "count_question": &lt;số câu hỏi con trong content&gt;,</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "3": "&lt;trap code cho dap an 3&gt;",</t>
+          <t xml:space="preserve">  "tag": "listen"</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "4": "&lt;trap code cho dap an 4&gt;"</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      }</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    }</t>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>Trường tùy chọn (OPTIONAL — chỉ thêm nếu cần phân tích chuyên sâu)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ],</t>
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>Các trường sau KHÔNG bắt buộc khi gen câu hỏi. Samples.json không chứa các trường này. Chỉ thêm khi user yêu cầu phân tích metadata:</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "level": 3,</t>
+          <t>// Trong content[]:</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "kind": "&lt;ma kind&gt;",</t>
+          <t>"question_feature": "&lt;mã từ bảng question_feature&gt;",</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "count_question": &lt;so cau hoi con trong content&gt;,</t>
+          <t>"difficulty": 3,</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "tag": "listen",</t>
+          <t>"distractor_traps": {</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "topic": "&lt;ma chu de tu bang topic&gt;"</t>
+          <t xml:space="preserve">  "1": "", "2": "trap_same_ending", "3": "trap_neg_없안", "4": "trap_shared_noun"</t>
         </is>
       </c>
     </row>
@@ -1715,694 +1720,662 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>Format bo sung cho kind co anh</t>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>// Ở cấp top-level:</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>Them truong q_image_description mo ta noi dung anh bang text:</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "q_image_description": {</t>
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>"topic": "daily_routine"</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>Format bổ sung cho kind có ảnh</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "1": "&lt;mo ta noi dung hinh 1&gt;",</t>
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>Thêm trường q_image_description mô tả nội dung ảnh bằng text:</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "2": "&lt;mo ta noi dung hinh 2&gt;",</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "3": "&lt;mo ta noi dung hinh 3&gt;",</t>
+          <t xml:space="preserve">  "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "4": "&lt;mo ta noi dung hinh 4&gt;"</t>
+          <t xml:space="preserve">    "1": "&lt;mô tả nội dung hình 1&gt;",</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }</t>
+          <t xml:space="preserve">    "2": "&lt;mô tả nội dung hình 2&gt;",</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>}</t>
+          <t xml:space="preserve">    "3": "&lt;mô tả nội dung hình 3&gt;",</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "4": "&lt;mô tả nội dung hình 4&gt;"</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>Voi kind 310002/3410003 (chi 1 buc tranh, dap an trong audio):</t>
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "q_image_description": {</t>
+          <t>}</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "image": "&lt;mo ta buc tranh duy nhat&gt;"</t>
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>Với kind 310002/3410003 (chỉ 1 bức tranh, đáp án trong audio):</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  "q_image_description": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "image": "&lt;mô tả bức tranh duy nhất&gt;"</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="11" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ Lưu ý: q_image_description là trường chỉ dùng khi gen câu hỏi mới — dùng để mô tả ảnh bằng text cho AI tạo ảnh sau. Trường này KHÔNG có trong samples.json (vì samples lấy từ dữ liệu thực đã có ảnh URL). Đặt ở cấp top-level của JSON (cùng cấp với title, general).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>Danh muc chu de (topic)</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="n"/>
-      <c r="C89" s="10" t="n"/>
-      <c r="D89" s="10" t="n"/>
-      <c r="E89" s="10" t="n"/>
-      <c r="F89" s="10" t="n"/>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="13" t="inlineStr">
-        <is>
-          <t>Chu de chung (ap dung cho EPS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="14" t="inlineStr">
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Danh mục chủ đề (topic)</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>Chủ đề chung (áp dụng cho EPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B91" s="14" t="inlineStr">
-        <is>
-          <t>Nhan tieng Anh</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="inlineStr">
-        <is>
-          <t>Tieng Han</t>
-        </is>
-      </c>
-      <c r="D91" s="14" t="inlineStr">
-        <is>
-          <t>Tu khoa nhan dien</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>`time_appointment`</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Time &amp; Appointments</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>시간/약속</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>시간, 약속, 오전, 오후, 언제, 몇 시</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>`workplace`</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Workplace &amp; Work</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>직장/업무</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>회사, 회의, 보고서, 출근, 퇴근, 팀장, 사장, 직장, 업무</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>`food_restaurant`</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Food &amp; Dining</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>음식/식당</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>식당, 밥, 먹다, 메뉴, 주문, 요리, 커피, 음식</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>`shopping_price`</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Shopping &amp; Price</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>쇼핑/가격</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>사다, 얼마, 할인, 비싸다, 마트, 백화점, 쇼핑</t>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>Tiếng Hàn</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>Từ khóa nhận diện</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>`health_hospital`</t>
+          <t>`time_appointment`</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Health &amp; Hospital</t>
+          <t>Time &amp; Appointments</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>건강/병원</t>
+          <t>시간/약속</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>병원, 아프다, 약, 의사, 운동, 진찰, 건강</t>
+          <t>시간, 약속, 오전, 오후, 언제, 몇 시</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>`weather_season`</t>
+          <t>`workplace`</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Weather &amp; Seasons</t>
+          <t>Workplace &amp; Work</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>날씨/계절</t>
+          <t>직장/업무</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>비, 눈, 덥다, 춥다, 날씨, 봄, 여름, 가을, 겨울</t>
+          <t>회사, 회의, 보고서, 출근, 퇴근, 팀장, 사장, 직장, 업무</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>`home_housing`</t>
+          <t>`food_restaurant`</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Home &amp; Housing</t>
+          <t>Food &amp; Dining</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>집/주거</t>
+          <t>음식/식당</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>집, 방, 아파트, 이사, 거실, 부엌</t>
+          <t>식당, 밥, 먹다, 메뉴, 주문, 요리, 커피, 음식</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>`transport`</t>
+          <t>`shopping_price`</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Shopping &amp; Price</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>교통/이동</t>
+          <t>쇼핑/가격</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>버스, 지하철, 택시, 역, 공항, 비행기, 기차, 교통</t>
+          <t>사다, 얼마, 할인, 비싸다, 마트, 백화점, 쇼핑</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>`hobby_leisure`</t>
+          <t>`health_hospital`</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Hobbies &amp; Leisure</t>
+          <t>Health &amp; Hospital</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>취미/여가</t>
+          <t>건강/병원</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>영화, 노래, 사진, 음악, 책, 등산, 수영, 취미</t>
+          <t>병원, 아프다, 약, 의사, 운동, 진찰, 건강</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>`travel`</t>
+          <t>`weather_season`</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Travel &amp; Tourism</t>
+          <t>Weather &amp; Seasons</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>여행/관광</t>
+          <t>날씨/계절</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>여행, 호텔, 예약, 관광지, 해외</t>
+          <t>비, 눈, 덥다, 춥다, 날씨, 봄, 여름, 가을, 겨울</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>`family_relations`</t>
+          <t>`home_housing`</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Family &amp; Relations</t>
+          <t>Home &amp; Housing</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>가족/관계</t>
+          <t>집/주거</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>가족, 엄마, 아빠, 결혼, 아이, 부모님</t>
+          <t>집, 방, 아파트, 이사, 거실, 부엌</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
+          <t>`transport`</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>교통/이동</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>버스, 지하철, 택시, 역, 공항, 비행기, 기차, 교통</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>`hobby_leisure`</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Hobbies &amp; Leisure</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>취미/여가</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>영화, 노래, 사진, 음악, 책, 등산, 수영, 취미</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>`travel`</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Travel &amp; Tourism</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>여행/관광</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>여행, 호텔, 예약, 관광지, 해외</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>`family_relations`</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Family &amp; Relations</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>가족/관계</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>가족, 엄마, 아빠, 결혼, 아이, 부모님</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
           <t>`phone_communication`</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>Phone &amp; Communication</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>전화/통신</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>전화, 번호, 메시지, 연락, 문자</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="13" t="inlineStr">
-        <is>
-          <t>Chu de rieng EPS-TOPIK (Level 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="11" t="inlineStr">
-        <is>
-          <t>Phat hien tu du lieu 2.242 cau EPS — cac chu de dac thu cho nguoi lao dong nuoc ngoai:</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="14" t="inlineStr">
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="13" t="inlineStr">
+        <is>
+          <t>Chủ đề riêng EPS-TOPIK (Level 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>Phát hiện từ dữ liệu 2.242 câu EPS — các chủ đề đặc thù cho người lao động nước ngoài:</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B107" s="14" t="inlineStr">
-        <is>
-          <t>Nhan tieng Anh</t>
-        </is>
-      </c>
-      <c r="C107" s="14" t="inlineStr">
-        <is>
-          <t>Tu khoa nhan dien</t>
-        </is>
-      </c>
-      <c r="D107" s="14" t="inlineStr">
-        <is>
-          <t>Ty le (L3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>Từ khóa nhận diện</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ (L3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>`factory_work`</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Factory &amp; Production</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>공장, 기계, 작업, 생산, 제품, 부품, 조립, 포장</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
+      <c r="D112" s="6" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>`dormitory_life`</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>Dormitory Life</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>기숙사, 룸메이트, 세탁기, 청소, 방, 규칙, 소음</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>`safety_workplace`</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Workplace Safety</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>안전, 사고, 위험, 보호, 장갑, 안전모, 소화기</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>`wages_contract`</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>Wages &amp; Contract</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>월급, 급여, 계약, 근무, 야근, 휴일, 수당</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="11" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>Chien luoc bay dap an sai (distractor_trap)</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="n"/>
-      <c r="C114" s="10" t="n"/>
-      <c r="D114" s="10" t="n"/>
-      <c r="E114" s="10" t="n"/>
-      <c r="F114" s="10" t="n"/>
-    </row>
-    <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="13" t="inlineStr">
-        <is>
-          <t>Nhom 1: Bay tu vung (Vocabulary Traps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="14" t="inlineStr">
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>Chiến lược bẫy đáp án sai (distractor_trap)</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="n"/>
+      <c r="C118" s="10" t="n"/>
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="10" t="n"/>
+      <c r="F118" s="10" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B116" s="14" t="inlineStr">
-        <is>
-          <t>Nhan tieng Anh</t>
-        </is>
-      </c>
-      <c r="C116" s="14" t="inlineStr">
-        <is>
-          <t>Mo ta</t>
-        </is>
-      </c>
-      <c r="D116" s="14" t="inlineStr">
-        <is>
-          <t>Bang chung tu du lieu</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>`trap_sound_similarity`</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>4 đáp án phát âm gần giống nhau</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>310001, 3410002</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>`trap_shared_noun`</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>Shared-Noun Trap</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>Dap an sai chua &gt;=2 danh tu giong audio</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>10.058 luot phat hien</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>`trap_sound_similarity`</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>Sound Similarity</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>4 dap an phat am gan giong nhau</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>100% o 310001/3410001/3410002. Tu don 2 am tiet chiem 85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>`trap_opposite_meaning`</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>Opposite Meaning</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>Dap an sai dung tu trai nghia voi dap an dung</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>15% o 210006/210007, 6% o 110006</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="13" t="inlineStr">
-        <is>
-          <t>Nhom 2: Bay phu dinh (Negation Traps)</t>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án sai chứa &gt;=2 danh từ giống audio</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>310004, 310005, 310006, 3410005</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B122" s="14" t="inlineStr">
-        <is>
-          <t>Nhan tieng Anh</t>
-        </is>
-      </c>
-      <c r="C122" s="14" t="inlineStr">
-        <is>
-          <t>Mo ta</t>
-        </is>
-      </c>
-      <c r="D122" s="14" t="inlineStr">
-        <is>
-          <t>Bang chung tu du lieu</t>
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>`trap_same_ending`</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Cả 4 đáp án kết thúc cùng dạng ngữ pháp</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>310001, 310004, 310005, 310006, 3410005</t>
         </is>
       </c>
     </row>
@@ -2414,992 +2387,969 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Negation 없/안/아니</t>
+          <t>Đáp án sai thêm 없다/안/아니다 để đảo nghĩa</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Dap an sai them 없다/안/아니다 de dao nghia</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>456 luot 없, 333 luot 안, 209 luot 아니</t>
+          <t>310001, 310004, 310005, 3410005</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>`trap_neg_않못`</t>
+          <t>`trap_subject_swap`</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>Negation 않/못</t>
+          <t>Gán hành động cho sai người (가↔나)</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Dap an sai them 않다/못하다 de phu dinh hanh dong</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>333 luot 않, 162 luot 못</t>
+          <t>310005, 310006</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>Nhom 3: Bay cau truc (Structural Traps)</t>
+          <t>Quy tắc gán nhãn bẫy</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="14" t="inlineStr">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>• Mỗi câu hỏi có thể có NHIỀU nhãn bẫy cùng lúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>• Gán nhãn dựa trên ĐÁP ÁN SAI, không phải đáp án đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>• Chỉ gán khi có bằng chứng rõ ràng, không suy đoán</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>Đặc điểm câu hỏi (question_feature)</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="n"/>
+      <c r="C131" s="10" t="n"/>
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="10" t="n"/>
+      <c r="F131" s="10" t="n"/>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="13" t="inlineStr">
+        <is>
+          <t>Nhóm câu hỏi có q_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B127" s="14" t="inlineStr">
-        <is>
-          <t>Nhan tieng Anh</t>
-        </is>
-      </c>
-      <c r="C127" s="14" t="inlineStr">
-        <is>
-          <t>Mo ta</t>
-        </is>
-      </c>
-      <c r="D127" s="14" t="inlineStr">
-        <is>
-          <t>Bang chung tu du lieu</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>`trap_same_ending`</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>Same-Ending Pattern</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>Ca 4 dap an ket thuc cung dang ngu phap</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>Pho bien nhat: ~ㅂ니다(907), ~있다(235), ~어요(185)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>`trap_same_start`</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>Same-Start Pattern</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>Ca 4 dap an bat dau bang cung mot tu</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>66 cau o 310004, 58 cau o 210007</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="13" t="inlineStr">
-        <is>
-          <t>Nhom 4: Bay noi dung (Content Traps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B132" s="14" t="inlineStr">
-        <is>
-          <t>Nhan tieng Anh</t>
-        </is>
-      </c>
-      <c r="C132" s="14" t="inlineStr">
-        <is>
-          <t>Mo ta</t>
-        </is>
-      </c>
-      <c r="D132" s="14" t="inlineStr">
-        <is>
-          <t>Bang chung tu du lieu</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>`trap_subject_swap`</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>Subject Swap</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>Gan hanh dong/y kien cho sai nguoi (가↔나)</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>1.026 luot swap_general</t>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn tiếng Anh</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>`trap_number_shift`</t>
+          <t>`qf_content_match`</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>Number/Time Shift</t>
+          <t>Content Match</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Thay doi con so/thoi gian tu audio</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>398 cau phat hien. Rat cao o 3410004-3410007(100%), 310006(52%)</t>
+          <t>"들은 내용으로 맞는 것을 고르십시오"</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>`trap_partial_truth`</t>
+          <t>`qf_what`</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>Partial Truth</t>
+          <t>What (General)</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>Dap an sai chua &gt;30% tu dung tu audio nhung bi sua 1 chi tiet</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>34% o 210004, 50% dap an sai 210006</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="22" customHeight="1">
-      <c r="A137" s="13" t="inlineStr">
-        <is>
-          <t>Quy tac gan nhan bay</t>
+          <t>"무엇입니까?", "무엇을 삽니까?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>`qf_what_doing`</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>What Doing</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>"무엇을 하고 있습니까?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>`qf_where`</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>Where/Which</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>"어디입니까?", "어느 나라?"</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="11" t="inlineStr">
-        <is>
-          <t>• Moi cau hoi co the co NHIEU nhan bay cung luc</t>
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>`qf_central_thought`</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>Central Thought</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>"중심 생각으로 맞는 것"</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="11" t="inlineStr">
-        <is>
-          <t>• Gan nhan dua tren DAP AN SAI, khong phai dap an dung</t>
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>`qf_why`</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Why/Reason</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>"왜?", "이유"</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="11" t="inlineStr">
-        <is>
-          <t>• Chi gan khi co bang chung ro rang, khong suy doan</t>
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>`qf_when_time`</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>When/Time</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>"언제?", "몇 시?", "얼마 동안?"</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="9" t="inlineStr">
-        <is>
-          <t>Dac diem cau hoi (question_feature)</t>
-        </is>
-      </c>
-      <c r="B142" s="10" t="n"/>
-      <c r="C142" s="10" t="n"/>
-      <c r="D142" s="10" t="n"/>
-      <c r="E142" s="10" t="n"/>
-      <c r="F142" s="10" t="n"/>
-    </row>
-    <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="13" t="inlineStr">
-        <is>
-          <t>Nhom cau hoi co q_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="14" t="inlineStr">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>`qf_who`</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>Who</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>"누구입니까?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>`qf_how_many`</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>How Many</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>"몇 명?", "몇 개?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>`qf_how_much`</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>How Much (Price)</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>"얼마입니까?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="13" t="inlineStr">
+        <is>
+          <t>Nhóm câu hỏi KHÔNG có q_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B144" s="14" t="inlineStr">
-        <is>
-          <t>Nhan tieng Anh</t>
-        </is>
-      </c>
-      <c r="C144" s="14" t="inlineStr">
-        <is>
-          <t>Mo ta</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>`qf_content_match`</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>Content Match</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>"들은 내용으로 맞는 것을 고르십시오"</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>`qf_what`</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>What (General)</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>"무엇입니까?", "무엇을 삽니까?"</t>
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>`qf_what_doing`</t>
+          <t>`qf_direct_qa`</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>What Doing</t>
+          <t>310004</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>"무엇을 하고 있습니까?"</t>
+          <t>Nghe câu hỏi -&gt; chọn câu trả lời trực tiếp</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>`qf_where`</t>
+          <t>`qf_next_utterance`</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>Where/Which</t>
+          <t>3410005</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>"어디입니까?", "어느 나라?"</t>
+          <t>Nghe hội thoại -&gt; chọn câu nối tiếp</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>`qf_central_thought`</t>
+          <t>`qf_match_image`</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>Central Thought</t>
+          <t>310003</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>"중심 생각으로 맞는 것"</t>
+          <t>Nghe -&gt; chọn hình khớp</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>`qf_why`</t>
+          <t>`qf_match_content`</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>Why/Reason</t>
+          <t>310005</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>"왜?", "이유"</t>
+          <t>Nghe -&gt; chọn phát biểu khớp nội dung</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>`qf_when_time`</t>
+          <t>`qf_identify_sound`</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>When/Time</t>
+          <t>310001</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>"언제?", "몇 시?", "얼마 동안?"</t>
+          <t>Nghe -&gt; nhận diện từ/câu</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>`qf_who`</t>
+          <t>`qf_identify_time`</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>Who</t>
+          <t>3410002</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>"누구입니까?"</t>
+          <t>Nghe giờ -&gt; chọn đồng hồ</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>`qf_how_many`</t>
+          <t>`qf_image_qa`</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>How Many</t>
+          <t>310002</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>"몇 명?", "몇 개?"</t>
+          <t>Nhìn hình + nghe 4 câu mô tả -&gt; chọn đúng</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>`qf_how_much`</t>
+          <t>`qf_multi_comprehension`</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>How Much (Price)</t>
+          <t>310006</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>"얼마입니까?"</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="13" t="inlineStr">
-        <is>
-          <t>Nhom cau hoi KHONG co q_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="14" t="inlineStr">
+          <t>Nghe dài và trả lời 2 câu hỏi</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc ngữ pháp trong audio (grammar_semantic)</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="n"/>
+      <c r="C157" s="10" t="n"/>
+      <c r="D157" s="10" t="n"/>
+      <c r="E157" s="10" t="n"/>
+      <c r="F157" s="10" t="n"/>
+    </row>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="13" t="inlineStr">
+        <is>
+          <t>Phân bố Level 3 (2.242 câu, chỉ liệt kê &gt;=5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>gram_honorific_시(21%), gram_request_세요(19%), gram_honorific_습니다(18%), gram_cause_니까(8%), gram_cond_면(7%), gram_contrast_는데(7%), gram_prog_고있(6%), gram_intent_겠(6%), gram_cause_어서(5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="13" t="inlineStr">
+        <is>
+          <t>Bảng nhãn ngữ pháp theo ý nghĩa (Level 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B157" s="14" t="inlineStr">
-        <is>
-          <t>Kind ap dung</t>
-        </is>
-      </c>
-      <c r="C157" s="14" t="inlineStr">
-        <is>
-          <t>Mo ta</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>`qf_direct_qa`</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>310004</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>Nghe cau hoi -&gt; chon cau tra loi truc tiep</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>`qf_next_utterance`</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>3410005</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>Nghe hoi thoai -&gt; chon cau noi tiep</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>`qf_match_image`</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
-        <is>
-          <t>310003</t>
-        </is>
-      </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>Nghe -&gt; chon hinh khop</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>`qf_match_content`</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>310005</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>Nghe -&gt; chon phat bieu khop noi dung</t>
+      <c r="B161" s="14" t="inlineStr">
+        <is>
+          <t>Cấu trúc</t>
+        </is>
+      </c>
+      <c r="C161" s="14" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+      <c r="D161" s="14" t="inlineStr">
+        <is>
+          <t>L3</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>`qf_identify_sound`</t>
+          <t>`gram_cause_어서`</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>310001</t>
+          <t>~어서/아서</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>Nghe -&gt; nhan dien tu/cau</t>
+          <t>Nguyên nhân (nhẹ)</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>`qf_identify_time`</t>
+          <t>`gram_cause_니까`</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>3410002</t>
+          <t>~니까</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>Nghe gio -&gt; chon dong ho</t>
+          <t>Nguyên nhân (nhấn mạnh)</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>8%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>`qf_image_qa`</t>
+          <t>`gram_cond_면`</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>310002</t>
+          <t>~(으)면</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>Nhin hinh + nghe 4 cau mo ta -&gt; chon dung</t>
+          <t>Điều kiện</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>`gram_contrast_지만`</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>~지만</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Đối lập trực tiếp</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>3%</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="22" customHeight="1">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t>Cau truc ngu phap trong audio (grammar_semantic)</t>
-        </is>
-      </c>
-      <c r="B167" s="10" t="n"/>
-      <c r="C167" s="10" t="n"/>
-      <c r="D167" s="10" t="n"/>
-      <c r="E167" s="10" t="n"/>
-      <c r="F167" s="10" t="n"/>
-    </row>
-    <row r="168" ht="22" customHeight="1">
-      <c r="A168" s="13" t="inlineStr">
-        <is>
-          <t>Phan bo Level 3 (2.242 cau, chi liet ke &gt;=5%)</t>
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>`gram_contrast_는데`</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>~는데/은데</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>Bối cảnh/đối lập mềm</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>`gram_intent_려고`</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>~(으)려고</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>Ý định</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>`gram_intent_겠`</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>~겠어요/겠습니다</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>Dự định/suy đoán</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="11" t="inlineStr">
-        <is>
-          <t>gram_honorific_시(21%), gram_request_세요(19%), gram_honorific_습니다(18%), gram_cause_니까(8%), gram_cond_면(7%), gram_contrast_는데(7%), gram_prog_고있(6%), gram_intent_겠(6%), gram_cause_어서(5%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="22" customHeight="1">
-      <c r="A170" s="13" t="inlineStr">
-        <is>
-          <t>Bang nhan ngu phap theo y nghia (Level 3)</t>
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>`gram_request_세요`</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>~(으)세요</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Yêu cầu lịch sự</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>`gram_request_주세요`</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>~주세요</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>Nhờ vả cụ thể</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>4%</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B171" s="14" t="inlineStr">
-        <is>
-          <t>Cau truc</t>
-        </is>
-      </c>
-      <c r="C171" s="14" t="inlineStr">
-        <is>
-          <t>Y nghia</t>
-        </is>
-      </c>
-      <c r="D171" s="14" t="inlineStr">
-        <is>
-          <t>L3</t>
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>`gram_prog_고있`</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>~고 있다</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>Đang diễn ra</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>`gram_cause_어서`</t>
+          <t>`gram_honorific_시`</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>~어서/아서</t>
+          <t>~시/셨/세요</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>Nguyen nhan (nhe)</t>
+          <t>Kính ngữ (시)</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>21%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>`gram_cause_니까`</t>
+          <t>`gram_honorific_습니다`</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>~니까</t>
+          <t>~습니다/ㅂ니다</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>Nguyen nhan (nhan manh)</t>
+          <t>Kính ngữ trang trọng</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="6" t="inlineStr">
-        <is>
-          <t>`gram_cond_면`</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
-        <is>
-          <t>~(으)면</t>
-        </is>
-      </c>
-      <c r="C174" s="6" t="inlineStr">
-        <is>
-          <t>Dieu kien</t>
-        </is>
-      </c>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>`gram_contrast_지만`</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>~지만</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>Doi lap truc tiep</t>
-        </is>
-      </c>
-      <c r="D175" s="6" t="inlineStr">
-        <is>
-          <t>3%</t>
+          <t>18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="13" t="inlineStr">
+        <is>
+          <t>Ngữ pháp trong đáp án (answer_grammar)</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>`gram_contrast_는데`</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>~는데/은데</t>
-        </is>
-      </c>
-      <c r="C176" s="6" t="inlineStr">
-        <is>
-          <t>Boi canh/doi lap mem</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr">
-        <is>
-          <t>7%</t>
+      <c r="A176" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B176" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="C176" s="14" t="inlineStr">
+        <is>
+          <t>Kind áp dụng</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>`gram_intent_려고`</t>
+          <t>`ans_word_phrase`</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>~(으)려고</t>
+          <t>Đáp án là từ đơn / cụm ngắn</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>Y dinh</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr">
-        <is>
-          <t>4%</t>
+          <t>310001</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>`gram_intent_겠`</t>
+          <t>`ans_formal_polite`</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>~겠어요/겠습니다</t>
+          <t>Đáp án dùng ~ㅂ니다/습니다</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>Du dinh/suy doan</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>6%</t>
+          <t>310002</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>`gram_request_세요`</t>
+          <t>`ans_image`</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>~(으)세요</t>
+          <t>Đáp án là hình ảnh</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>Yeu cau lich su</t>
-        </is>
-      </c>
-      <c r="D179" s="6" t="inlineStr">
-        <is>
-          <t>19%</t>
+          <t>310003, 3410002</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>`gram_request_주세요`</t>
+          <t>`ans_formal`</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>~주세요</t>
+          <t>Đáp án dùng ~ㅂ니다</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>Nho va cu the</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t>4%</t>
+          <t>310004, 310005, 310006</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>`gram_prog_고있`</t>
+          <t>`ans_informal_polite`</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>~고 있다</t>
+          <t>Đáp án dùng ~아/어요</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>Dang dien ra</t>
-        </is>
-      </c>
-      <c r="D181" s="6" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="6" t="inlineStr">
-        <is>
-          <t>`gram_honorific_시`</t>
-        </is>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
-        <is>
-          <t>~시/셨/세요</t>
-        </is>
-      </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>Kinh ngu (시)</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>21%</t>
+          <t>3410005</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="6" t="inlineStr">
-        <is>
-          <t>`gram_honorific_습니다`</t>
-        </is>
-      </c>
-      <c r="B183" s="6" t="inlineStr">
-        <is>
-          <t>~습니다/ㅂ니다</t>
-        </is>
-      </c>
-      <c r="C183" s="6" t="inlineStr">
-        <is>
-          <t>Kinh ngu trang trong</t>
-        </is>
-      </c>
-      <c r="D183" s="6" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="13" t="inlineStr">
-        <is>
-          <t>Ngu phap trong dap an (answer_grammar)</t>
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc audio (audio_format)</t>
+        </is>
+      </c>
+      <c r="B184" s="10" t="n"/>
+      <c r="C184" s="10" t="n"/>
+      <c r="D184" s="10" t="n"/>
+      <c r="E184" s="10" t="n"/>
+      <c r="F184" s="10" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B185" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="C185" s="14" t="inlineStr">
+        <is>
+          <t>Kind chính</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B186" s="14" t="inlineStr">
-        <is>
-          <t>Mo ta</t>
-        </is>
-      </c>
-      <c r="C186" s="14" t="inlineStr">
-        <is>
-          <t>Kind ap dung</t>
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>`audio_dialog_가나`</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>Hội thoại 가/나 (EPS)</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>310003-310006</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>`ans_formal`</t>
+          <t>`audio_single_word`</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>Dap an dung ~ㅂ니다</t>
+          <t>Từ đơn/cụm ngắn (&lt;15 ký tự)</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>310004, 310005, 310006, va cac EPS kinds</t>
+          <t>310001, 3410002</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>`ans_short_word`</t>
+          <t>`audio_single_sentence`</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>Dap an la tu don / cum ngan</t>
+          <t>Câu đơn (15-50 ký tự)</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>310001, 3410002</t>
+          <t>310004, 3410005</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>`ans_sentence`</t>
+          <t>`audio_numbered`</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>Dap an la cau day du</t>
+          <t>4 câu mô tả đánh số (1. 2. 3. 4.)</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>3410005, 310003</t>
+          <t>310002</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3363,7 @@
     <row r="192" ht="22" customHeight="1">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>Cau truc audio (audio_format)</t>
+          <t>Thang đo khó (Difficulty Scale) — EPS kinds only</t>
         </is>
       </c>
       <c r="B192" s="10" t="n"/>
@@ -3425,751 +3375,650 @@
     <row r="193">
       <c r="A193" s="14" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Mức</t>
         </is>
       </c>
       <c r="B193" s="14" t="inlineStr">
         <is>
-          <t>Mo ta</t>
+          <t>Kind</t>
         </is>
       </c>
       <c r="C193" s="14" t="inlineStr">
         <is>
-          <t>Kind chinh</t>
+          <t>Kiểu suy luận</t>
+        </is>
+      </c>
+      <c r="D193" s="14" t="inlineStr">
+        <is>
+          <t>Nhãn</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>`audio_dialog_가나`</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>Hoi thoai 가/나 (EPS)</t>
+          <t>310001, 3410002</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>310003-310006</t>
+          <t>`sound_recognition` / `time_recognition`</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>Nhận diện từ/giờ</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>`audio_single_word`</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>Tu don/cum ngan (&lt;15 ky tu)</t>
+          <t>310004, 310002</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>310001, 3410002</t>
+          <t>`direct_match` / `image_qa`</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>Hỏi-đáp đơn giản</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>`audio_single_sentence`</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>Cau don (15-50 ky tu)</t>
+          <t>3410005</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>310004, 3410005</t>
+          <t>`pragmatic_response`</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>Chọn câu nối tiếp</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>`audio_numbered`</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>4 cau mo ta danh so (1. 2. 3. 4.)</t>
+          <t>310003</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>310002</t>
+          <t>`scene_matching`</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>Chọn hình liên quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>310005</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>`detail_extraction`</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>Trích xuất chi tiết</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="9" t="inlineStr">
-        <is>
-          <t>Thang do kho (Difficulty Scale) — EPS kinds only</t>
-        </is>
-      </c>
-      <c r="B200" s="10" t="n"/>
-      <c r="C200" s="10" t="n"/>
-      <c r="D200" s="10" t="n"/>
-      <c r="E200" s="10" t="n"/>
-      <c r="F200" s="10" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="14" t="inlineStr">
-        <is>
-          <t>Muc</t>
-        </is>
-      </c>
-      <c r="B201" s="14" t="inlineStr">
-        <is>
-          <t>Kind</t>
-        </is>
-      </c>
-      <c r="C201" s="14" t="inlineStr">
-        <is>
-          <t>Kieu suy luan</t>
-        </is>
-      </c>
-      <c r="D201" s="14" t="inlineStr">
-        <is>
-          <t>Nhan</t>
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>310006</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>`multi_comprehension`</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>2 câu hỏi / đoạn dài</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="22" customHeight="1">
+      <c r="A201" s="13" t="inlineStr">
+        <is>
+          <t>Mô tả kiểu suy luận (reasoning_type)</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>310001, 3410002</t>
-        </is>
-      </c>
-      <c r="C202" s="6" t="inlineStr">
-        <is>
-          <t>`sound_recognition` / `time_recognition`</t>
-        </is>
-      </c>
-      <c r="D202" s="6" t="inlineStr">
-        <is>
-          <t>Nhan dien tu/gio</t>
+      <c r="A202" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B202" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>`sound_recognition`</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>310004, 310002</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>`direct_match` / `image_qa`</t>
-        </is>
-      </c>
-      <c r="D203" s="6" t="inlineStr">
-        <is>
-          <t>Hoi-dap don gian</t>
+          <t>Nhận diện chính xác từ/câu được nghe</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>`time_recognition`</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>3410005</t>
-        </is>
-      </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>`pragmatic_response`</t>
-        </is>
-      </c>
-      <c r="D204" s="6" t="inlineStr">
-        <is>
-          <t>Chon cau noi tiep</t>
+          <t>Nghe giờ, chọn đồng hồ phù hợp</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>`direct_match`</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>310003</t>
-        </is>
-      </c>
-      <c r="C205" s="6" t="inlineStr">
-        <is>
-          <t>`scene_matching`</t>
-        </is>
-      </c>
-      <c r="D205" s="6" t="inlineStr">
-        <is>
-          <t>Chon hinh lien quan</t>
+          <t>Ghép câu hỏi với câu trả lời trực tiếp</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>`image_qa`</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>310005</t>
-        </is>
-      </c>
-      <c r="C206" s="6" t="inlineStr">
-        <is>
-          <t>`detail_extraction`</t>
-        </is>
-      </c>
-      <c r="D206" s="6" t="inlineStr">
-        <is>
-          <t>Trich xuat chi tiet</t>
+          <t>Nhìn hình, nghe câu hỏi + đáp án, chọn đúng</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>`pragmatic_response`</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>310006</t>
-        </is>
-      </c>
-      <c r="C207" s="6" t="inlineStr">
+          <t>Chọn phản hồi phù hợp ngữ cảnh giao tiếp</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>`scene_matching`</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>Nghe audio, chọn bức tranh minh họa khớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>`detail_extraction`</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>Trích xuất chi tiết cụ thể từ hội thoại</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>`multi_comprehension`</t>
         </is>
       </c>
-      <c r="D207" s="6" t="inlineStr">
-        <is>
-          <t>2 cau hoi / doan dai</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="22" customHeight="1">
-      <c r="A209" s="13" t="inlineStr">
-        <is>
-          <t>Mo ta kieu suy luan (reasoning_type)</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B210" s="14" t="inlineStr">
-        <is>
-          <t>Mo ta</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="6" t="inlineStr">
-        <is>
-          <t>`sound_recognition`</t>
-        </is>
-      </c>
-      <c r="B211" s="6" t="inlineStr">
-        <is>
-          <t>Nhan dien chinh xac tu/cau duoc nghe</t>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>Trả lời 2 câu hỏi từ 1 đoạn</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr">
-        <is>
-          <t>`time_recognition`</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
-        <is>
-          <t>Nghe gio, chon dong ho phu hop</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>`direct_match`</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
-        <is>
-          <t>Ghep cau hoi voi cau tra loi truc tiep</t>
-        </is>
-      </c>
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="22" customHeight="1">
+      <c r="A213" s="9" t="inlineStr">
+        <is>
+          <t>Cấp độ giao tiếp trong audio (speech_level)</t>
+        </is>
+      </c>
+      <c r="B213" s="10" t="n"/>
+      <c r="C213" s="10" t="n"/>
+      <c r="D213" s="10" t="n"/>
+      <c r="E213" s="10" t="n"/>
+      <c r="F213" s="10" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>`image_qa`</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
-        <is>
-          <t>Nhin hinh, nghe cau hoi + dap an, chon dung</t>
+      <c r="A214" s="14" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B214" s="14" t="inlineStr">
+        <is>
+          <t>Audio chính</t>
+        </is>
+      </c>
+      <c r="C214" s="14" t="inlineStr">
+        <is>
+          <t>Đáp án</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>`pragmatic_response`</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>Chon phan hoi phu hop ngu canh giao tiep</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>`scene_matching`</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
-        <is>
-          <t>Nghe audio, chon buc tranh minh hoa khop</t>
+          <t>`informal_polite` 37%, `modifier` 31%, `connective` 16%</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>`formal_polite` (~ㅂ니다) cho EPS</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>`detail_extraction`</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
-        <is>
-          <t>Trich xuat chi tiet cu the tu hoi thoai</t>
+      <c r="A217" s="11" t="inlineStr">
+        <is>
+          <t>Quy tắc: Audio EPS dùng informal_polite là chính. Đáp án EPS thường dùng formal_polite (~ㅂ니다) — xem answer_grammar ans_formal.</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="6" t="inlineStr">
-        <is>
-          <t>`multi_comprehension`</t>
-        </is>
-      </c>
-      <c r="B218" s="6" t="inlineStr">
-        <is>
-          <t>Tra loi 2 cau hoi tu 1 doan</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="11" t="inlineStr">
+      <c r="A218" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="22" customHeight="1">
-      <c r="A221" s="9" t="inlineStr">
-        <is>
-          <t>Cap do giao tiep trong audio (speech_level)</t>
-        </is>
-      </c>
-      <c r="B221" s="10" t="n"/>
-      <c r="C221" s="10" t="n"/>
-      <c r="D221" s="10" t="n"/>
-      <c r="E221" s="10" t="n"/>
-      <c r="F221" s="10" t="n"/>
+    <row r="219" ht="22" customHeight="1">
+      <c r="A219" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc chung khi gen câu hỏi</t>
+        </is>
+      </c>
+      <c r="B219" s="10" t="n"/>
+      <c r="C219" s="10" t="n"/>
+      <c r="D219" s="10" t="n"/>
+      <c r="E219" s="10" t="n"/>
+      <c r="F219" s="10" t="n"/>
+    </row>
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="13" t="inlineStr">
+        <is>
+          <t>1. Chất lượng nội dung tiếng Hàn</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="11" t="inlineStr">
+        <is>
+          <t>• Dùng ngữ pháp đúng Level 3 (xem bảng speech_level + grammar_semantic)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="14" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="B222" s="14" t="inlineStr">
-        <is>
-          <t>Audio chinh</t>
-        </is>
-      </c>
-      <c r="C222" s="14" t="inlineStr">
-        <is>
-          <t>Dap an</t>
+      <c r="A222" s="11" t="inlineStr">
+        <is>
+          <t>• Hội thoại tự nhiên, đa dạng chủ đề đời sống + lao động</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B223" s="6" t="inlineStr">
-        <is>
-          <t>`informal_polite` 37%, `modifier` 31%, `connective` 16%</t>
-        </is>
-      </c>
-      <c r="C223" s="6" t="inlineStr">
-        <is>
-          <t>`formal_polite` (~ㅂ니다) cho EPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="11" t="inlineStr">
-        <is>
-          <t>Quy tac: Audio EPS dung informal_polite la chinh. Dap an EPS thuong dung formal_polite (~ㅂ니다) — xem answer_grammar ans_formal.</t>
+      <c r="A223" s="11" t="inlineStr">
+        <is>
+          <t>• KHÔNG lặp lại từ vựng/ngữ cảnh giữa các câu trong cùng batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="11" t="inlineStr">
+        <is>
+          <t>• Pha trộn chủ đề chung + chủ đề EPS đặc thù</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="22" customHeight="1">
+      <c r="A225" s="13" t="inlineStr">
+        <is>
+          <t>2. Xây dựng đáp án sai (distractor)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="22" customHeight="1">
-      <c r="A227" s="9" t="inlineStr">
-        <is>
-          <t>Quy tac chung khi gen cau hoi</t>
-        </is>
-      </c>
-      <c r="B227" s="10" t="n"/>
-      <c r="C227" s="10" t="n"/>
-      <c r="D227" s="10" t="n"/>
-      <c r="E227" s="10" t="n"/>
-      <c r="F227" s="10" t="n"/>
-    </row>
-    <row r="228" ht="22" customHeight="1">
-      <c r="A228" s="13" t="inlineStr">
-        <is>
-          <t>1. Chat luong noi dung tieng Han</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="11" t="inlineStr">
-        <is>
-          <t>• Dung ngu phap dung Level 3 (xem bang speech_level + grammar_semantic)</t>
+          <t>• Tuân theo tỷ lệ bẫy của từng kind (xem file kind tương ứng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="11" t="inlineStr">
+        <is>
+          <t>• Phải hợp lý nhưng SAI về nội dung</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="11" t="inlineStr">
+        <is>
+          <t>• Tái sử dụng từ vựng audio khi kind yêu cầu shared_word</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="22" customHeight="1">
+      <c r="A229" s="13" t="inlineStr">
+        <is>
+          <t>3. Giải thích (explain)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>• Hoi thoai tu nhien, da dang chu de doi song + lao dong</t>
+          <t>• vi: Dịch cả 4 đáp án -&gt; dấu -------------------- -&gt; giải thích đáp án đúng, ghi chú trap type cho từng đáp án sai</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>• KHONG lap lai tu vung/ngu canh giua cac cau trong cung batch</t>
+          <t>• en: Tương tự bằng tiếng Anh</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t>• Pha tron chu de chung + chu de EPS dac thu</t>
+          <t>• Highlight từ vựng/ngữ pháp quan trọng</t>
         </is>
       </c>
     </row>
     <row r="233" ht="22" customHeight="1">
       <c r="A233" s="13" t="inlineStr">
         <is>
-          <t>2. Xay dung dap an sai (distractor)</t>
+          <t>4. Số lượng</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>• Tuan theo ty le bay cua tung kind (xem file kind tuong ung)</t>
+          <t>• Mặc định: 5 câu mỗi kind nếu user không chỉ định</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>• Phai hop ly nhung SAI ve noi dung</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="11" t="inlineStr">
-        <is>
-          <t>• Tai su dung tu vung audio khi kind yeu cau shared_word</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="22" customHeight="1">
-      <c r="A237" s="13" t="inlineStr">
-        <is>
-          <t>3. Giai thich (explain)</t>
+          <t>• Tối đa: 20 câu mỗi lần</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="22" customHeight="1">
+      <c r="A236" s="13" t="inlineStr">
+        <is>
+          <t>5. Kiểm tra sau khi gen (Validation Checklist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] q_correct nằm trong 1-4</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>• vi: Dich ca 4 dap an -&gt; dau -------------------- -&gt; giai thich dap an dung, ghi chu trap type cho tung dap an sai</t>
+          <t>• [ ] 4 đáp án không trùng nhau</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t>• en: Tuong tu bang tieng Anh</t>
+          <t>• [ ] Audio là tiếng Hàn tự nhiên</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>• Highlight tu vung/ngu phap quan trong</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="22" customHeight="1">
-      <c r="A241" s="13" t="inlineStr">
-        <is>
-          <t>4. So luong</t>
+          <t>• [ ] Ngữ pháp đúng Level 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] Bẫy đúng phân bố của kind</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>• Mac dinh: 5 cau moi kind neu user khong chi dinh</t>
+          <t>• [ ] Bản dịch (vi/en) chính xác</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>• Toi da: 20 cau moi lan</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="22" customHeight="1">
-      <c r="A244" s="13" t="inlineStr">
-        <is>
-          <t>5. Kiem tra sau khi gen (Validation Checklist)</t>
+          <t>• [ ] explain chứa dịch 4 đáp án + lý do đáp án đúng + trap type cho đáp án sai</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] count_question khớp số phần tử trong content</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>• [ ] q_correct nam trong 1-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="11" t="inlineStr">
-        <is>
-          <t>• [ ] 4 dap an khong trung nhau</t>
-        </is>
-      </c>
+          <t>• [ ] level luôn = 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="22" customHeight="1">
+      <c r="A246" s="9" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B246" s="10" t="n"/>
+      <c r="C246" s="10" t="n"/>
+      <c r="D246" s="10" t="n"/>
+      <c r="E246" s="10" t="n"/>
+      <c r="F246" s="10" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Audio la tieng Han tu nhien</t>
+          <t>1. User chỉ định kind -&gt; đọc file kinds/{kind}.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Ngu phap dung Level 3</t>
+          <t>2. Hỏi số lượng (mặc định 5)</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Bay dung phan bo cua kind</t>
+          <t>3. Gen câu hỏi theo JSON format + quy tắc kind + chiến lược bẫy</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Ban dich (vi/en) chinh xac</t>
+          <t>4. Lưu JSON tạm -&gt; chạy scripts/save_listen.py để tách CSV theo kind</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t>• [ ] explain chua dich 4 dap an + ly do dap an dung + trap type cho dap an sai</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="11" t="inlineStr">
-        <is>
-          <t>• [ ] count_question khop so phan tu trong content</t>
+          <t>5. Validate theo checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="1">
+      <c r="A252" s="13" t="inlineStr">
+        <is>
+          <t>Lưu kết quả bằng script</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="11" t="inlineStr">
-        <is>
-          <t>• [ ] level luon = 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="22" customHeight="1">
-      <c r="A254" s="9" t="inlineStr">
-        <is>
-          <t>Workflow</t>
-        </is>
-      </c>
-      <c r="B254" s="10" t="n"/>
-      <c r="C254" s="10" t="n"/>
-      <c r="D254" s="10" t="n"/>
-      <c r="E254" s="10" t="n"/>
-      <c r="F254" s="10" t="n"/>
+      <c r="A253" s="12" t="inlineStr">
+        <is>
+          <t># Lưu CSV theo kind + JSON + merge tổng</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="12" t="inlineStr">
+        <is>
+          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py gen_temp.json -o output/listen-eps --json --merge</t>
+        </is>
+      </c>
     </row>
     <row r="255">
-      <c r="A255" s="11" t="inlineStr">
-        <is>
-          <t>1. User chi dinh kind -&gt; doc file kinds/{kind}.md</t>
-        </is>
-      </c>
+      <c r="A255" s="12" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="11" t="inlineStr">
-        <is>
-          <t>2. Hoi so luong (mac dinh 5)</t>
+      <c r="A256" s="12" t="inlineStr">
+        <is>
+          <t># Chỉ validate</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="11" t="inlineStr">
-        <is>
-          <t>3. Gen cau hoi theo JSON format + quy tac kind + chien luoc bay</t>
+      <c r="A257" s="12" t="inlineStr">
+        <is>
+          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py gen_temp.json --validate-only</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="11" t="inlineStr">
-        <is>
-          <t>4. Luu JSON tam -&gt; chay scripts/save_listen.py de tach CSV theo kind</t>
-        </is>
-      </c>
+      <c r="A258" s="12" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="11" t="inlineStr">
-        <is>
-          <t>5. Validate theo checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="22" customHeight="1">
-      <c r="A260" s="13" t="inlineStr">
-        <is>
-          <t>Luu ket qua bang script</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="12" t="inlineStr">
-        <is>
-          <t># Luu CSV theo kind + JSON + merge tong</t>
+      <c r="A259" s="12" t="inlineStr">
+        <is>
+          <t># Append thêm batch mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="12" t="inlineStr">
+        <is>
+          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py new_batch.json --append</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="12" t="inlineStr">
-        <is>
-          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py gen_temp.json -o output/listen-eps --json --merge</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="12" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="12" t="inlineStr">
-        <is>
-          <t># Chi validate</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="12" t="inlineStr">
-        <is>
-          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py gen_temp.json --validate-only</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="12" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="12" t="inlineStr">
-        <is>
-          <t># Append them batch moi</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="12" t="inlineStr">
-        <is>
-          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py new_batch.json --append</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="11" t="inlineStr">
+      <c r="A262" s="11" t="inlineStr">
         <is>
           <t>Output: output/listen-eps/level_3/{kind}.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="159">
+  <mergeCells count="158">
+    <mergeCell ref="A183:F183"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A118:F118"/>
     <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A158:F158"/>
     <mergeCell ref="A238:F238"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
@@ -4177,17 +4026,16 @@
     <mergeCell ref="A86:F86"/>
     <mergeCell ref="A239:F239"/>
     <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A175:F175"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A263:F263"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A224:F224"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A200:F200"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A265:F265"/>
-    <mergeCell ref="A121:F121"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A249:F249"/>
@@ -4201,10 +4049,8 @@
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A226:F226"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A266:F266"/>
     <mergeCell ref="A82:F82"/>
     <mergeCell ref="A260:F260"/>
-    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A241:F241"/>
     <mergeCell ref="A250:F250"/>
@@ -4213,18 +4059,19 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A212:F212"/>
     <mergeCell ref="A243:F243"/>
+    <mergeCell ref="A221:F221"/>
     <mergeCell ref="A252:F252"/>
-    <mergeCell ref="A221:F221"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A236:F236"/>
-    <mergeCell ref="A267:F267"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A223:F223"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A213:F213"/>
     <mergeCell ref="A126:F126"/>
-    <mergeCell ref="A141:F141"/>
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="A259:F259"/>
     <mergeCell ref="A22:F22"/>
@@ -4233,35 +4080,30 @@
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A240:F240"/>
     <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A199:F199"/>
     <mergeCell ref="A230:F230"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A167:F167"/>
+    <mergeCell ref="A127:F127"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A114:F114"/>
     <mergeCell ref="A232:F232"/>
     <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A142:F142"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A191:F191"/>
-    <mergeCell ref="A169:F169"/>
     <mergeCell ref="A225:F225"/>
     <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A218:F218"/>
     <mergeCell ref="A227:F227"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A137:F137"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A268:F268"/>
+    <mergeCell ref="A217:F217"/>
     <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A105:F105"/>
     <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A139:F139"/>
     <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A129:F129"/>
     <mergeCell ref="A242:F242"/>
     <mergeCell ref="A251:F251"/>
     <mergeCell ref="A76:F76"/>
@@ -4269,62 +4111,65 @@
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A131:F131"/>
     <mergeCell ref="A244:F244"/>
-    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A253:F253"/>
     <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A109:F109"/>
     <mergeCell ref="A231:F231"/>
-    <mergeCell ref="A253:F253"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A117:F117"/>
     <mergeCell ref="A229:F229"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A245:F245"/>
-    <mergeCell ref="A270:F270"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A157:F157"/>
     <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A166:F166"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A256:F256"/>
+    <mergeCell ref="A87:F87"/>
     <mergeCell ref="A65:F65"/>
     <mergeCell ref="A246:F246"/>
+    <mergeCell ref="A128:F128"/>
     <mergeCell ref="A255:F255"/>
-    <mergeCell ref="A264:F264"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A233:F233"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A89:F89"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A192:F192"/>
     <mergeCell ref="A248:F248"/>
     <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A235:F235"/>
     <mergeCell ref="A247:F247"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A219:F219"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A106:F106"/>
     <mergeCell ref="A234:F234"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A184:F184"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A156:F156"/>
-    <mergeCell ref="A170:F170"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A67:F67"/>
     <mergeCell ref="A220:F220"/>
+    <mergeCell ref="A130:F130"/>
     <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A261:F261"/>
-    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A201:F201"/>
+    <mergeCell ref="A222:F222"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A110:F110"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A69:F69"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4337,7 +4182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4554,262 +4399,274 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>answer_grammar</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>`ans_word_phrase`</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Chiến lược bẫy</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Bẫy</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>`trap_sound_similarity`</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>**LUÔN LUÔN**. Cả 4 đáp án có âm tương tự nhau</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>`trap_same_ending`</t>
+          <t>`trap_sound_similarity`</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Các từ kết thúc giống nhau</t>
+          <t>**LUÔN LUÔN**. Cả 4 đáp án có âm tương tự nhau</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t>`trap_same_ending`</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Các từ kết thúc giống nhau</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>`trap_neg_없안`</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Từ phủ định gây nhầm</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>• Một từ đơn hoặc cụm từ rất ngắn tiếng Hàn (1-2 âm tiết)</t>
-        </is>
-      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>• Ví dụ: "우유", "회사", "아침"</t>
+          <t>• Một từ đơn hoặc cụm từ rất ngắn tiếng Hàn (1-2 âm tiết)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
+          <t>• Ví dụ: "우유", "회사", "아침"</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
           <t>• Format: từ đơn, không có người nói, không có ngữ cảnh</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>• 4 từ tiếng Hàn phát âm tương tự</t>
-        </is>
-      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>• q_text: rỗng</t>
+          <t>• 4 từ tiếng Hàn phát âm tương tự</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>• q_image: rỗng</t>
+          <t>• q_text: rỗng</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: từ được phát trong audio</t>
+          <t>• q_image: rỗng</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án sai: 3 từ có mẫu nguyên âm/phụ âm tương tự gây nhầm lẫn</t>
+          <t>• Đáp án đúng: từ được phát trong audio</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>• 310001: đáp án dạng text thuần (e.g., ['우유', '오이', '아이', '이유'])</t>
+          <t>• Đáp án sai: 3 từ có mẫu nguyên âm/phụ âm tương tự gây nhầm lẫn</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>• 310001: đáp án dạng text thuần (e.g., ['우유', '오이', '아이', '이유'])</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
           <t>• 3410001: đáp án có số thứ tự prefix (e.g., ['1. 우유', '2. 오이', '3. 아이', '4. 이유'])</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Quy tắc bắt buộc</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>1. 4 từ PHẢI có mẫu nguyên âm/phụ âm tương tự để tạo sự nhầm lẫn</t>
-        </is>
-      </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>2. Ưu tiên các cặp từ dễ nghe nhầm (ㅗ↔ㅜ, ㅏ↔ㅓ, ㄱ↔ㅋ, ㅂ↔ㅍ)</t>
+          <t>1. 4 từ PHẢI có mẫu nguyên âm/phụ âm tương tự để tạo sự nhầm lẫn</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
+          <t>2. Ưu tiên các cặp từ dễ nghe nhầm (ㅗ↔ㅜ, ㅏ↔ㅓ, ㄱ↔ㅋ, ㅂ↔ㅍ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
           <t>3. Từ phải thuộc vốn từ vựng EPS cơ bản</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>Audio: "우유"</t>
-        </is>
-      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>Đáp án (310001): ① 우유 ② 오이 ③ 아이 ④ 이유</t>
+          <t>Audio: "우유"</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>Đáp án (3410001): 1. 우유  2. 오이  3. 아이  4. 이유</t>
+          <t>Đáp án (310001): ① 우유 ② 오이 ③ 아이 ④ 이유</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>Đúng: ① (từ nghe được là "우유")</t>
+          <t>Đáp án (3410001): 1. 우유  2. 오이  3. 아이  4. 이유</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>Audio: "회사"</t>
+          <t>Đúng: ① (từ nghe được là "우유")</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Audio: "회사"</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>Audio: "아침"</t>
         </is>
@@ -4827,15 +4684,14 @@
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
@@ -4845,6 +4701,7 @@
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
@@ -4859,7 +4716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5088,408 +4945,420 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>answer_grammar</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>`ans_formal_polite`</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Chiến lược bẫy</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Không phát hiện bẫy rõ — đáp án nằm trong audio, không phải text options.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>• 4 câu mô tả được đọc to (đánh số 1-4), mô tả điều có thể đang xảy ra trong hình</t>
-        </is>
-      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
+          <t>• 4 câu mô tả được đọc to (đánh số 1-4), mô tả điều có thể đang xảy ra trong hình</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>• Format:</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. 식사를 하고 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. 빨래를 하고 있습니다.</t>
+          <t xml:space="preserve">  1. 식사를 하고 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. 머리를 자르고 있습니다.</t>
+          <t xml:space="preserve">  2. 빨래를 하고 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  3. 머리를 자르고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  4. 김치를 만들고 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>• q_answer: ["1. ", "2. ", "3. ", "4. "] (310002) hoặc ["1.", "2.", "3.", "4."] (3410003) — đáp án nằm trong audio</t>
-        </is>
-      </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>• q_text: có câu hỏi về hình (e.g., "사람들이 무엇을 하고 있습니까?")</t>
+          <t>• q_answer: ["1. ", "2. ", "3. ", "4. "] (310002) hoặc ["1.", "2.", "3.", "4."] (3410003) — đáp án nằm trong audio</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
+          <t>• q_text: có câu hỏi về hình (e.g., "사람들이 무엇을 하고 있습니까?")</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
           <t>• q_image: có (1 ảnh mỗi câu)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Phân loại q_text (8 dạng)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Dạng</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Số câu</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>Ví dụ</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>`object_what`</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>이것은 무엇입니까?</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>`action_doing`</t>
+          <t>`object_what`</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>이 사람은 무엇을 하고 있습니까?</t>
+          <t>이것은 무엇입니까?</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>`place_where`</t>
+          <t>`action_doing`</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>여기는 어디입니까?</t>
+          <t>이 사람은 무엇을 하고 있습니까?</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>`date_when`</t>
+          <t>`place_where`</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>언제입니까?</t>
+          <t>여기는 어디입니까?</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>`object_job`</t>
+          <t>`date_when`</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>이 사람의 직업은 무엇입니까?</t>
+          <t>언제입니까?</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>`weather`</t>
+          <t>`object_job`</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>날씨가 어떻습니까?</t>
+          <t>이 사람의 직업은 무엇입니까?</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>`count`</t>
+          <t>`weather`</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>몇 개입니까?</t>
+          <t>날씨가 어떻습니까?</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
+          <t>`count`</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>몇 개입니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
           <t>`quality`</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>어떤 것입니까?</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Mỗi câu có 1 bức tranh. Dùng key "image" để mô tả cảnh trong hình.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Quy tắc tạo audio và hình</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>1. Hình phải mô tả cảnh rõ ràng, dễ nhận biết</t>
-        </is>
-      </c>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>2. Audio gồm 1 câu đúng + 3 câu hợp lý nhưng sai so với hình</t>
+          <t>1. Hình phải mô tả cảnh rõ ràng, dễ nhận biết</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
+          <t>2. Audio gồm 1 câu đúng + 3 câu hợp lý nhưng sai so với hình</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
           <t>3. 3 câu sai phải liên quan đến cùng chủ đề nhưng khác hành động/đối tượng/địa điểm</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "g_text_audio": "1. 식사를 하고 있습니다.\n2. 빨래를 하고 있습니다.\n3. 머리를 자르고 있습니다.\n4. 김치를 만들고 있습니다.",</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "content": [{</t>
+          <t xml:space="preserve">  "g_text_audio": "1. 식사를 하고 있습니다.\n2. 빨래를 하고 있습니다.\n3. 머리를 자르고 있습니다.\n4. 김치를 만들고 있습니다.",</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_text": "사람들이 무엇을 하고 있습니까?",</t>
+          <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_image_description": {</t>
+          <t xml:space="preserve">    "q_text": "사람들이 무엇을 하고 있습니까?",</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "image": "여자가 부엌에서 빨래를 하고 있다. 세탁기 옆에 빨래 바구니가 있다."</t>
+          <t xml:space="preserve">    "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">      "image": "여자가 부엌에서 빨래를 하고 있다. 세탁기 옆에 빨래 바구니가 있다."</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_answer": ["1. ", "2. ", "3. ", "4. "],</t>
+          <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 2</t>
+          <t xml:space="preserve">    "q_answer": ["1. ", "2. ", "3. ", "4. "],</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">    "q_correct": 2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>}</t>
         </is>
@@ -5499,6 +5368,7 @@
   <mergeCells count="39">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A66:F66"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A18:F18"/>
@@ -5508,15 +5378,15 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A65:F65"/>
@@ -5524,7 +5394,6 @@
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A59:F59"/>
@@ -5547,7 +5416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5776,248 +5645,260 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>answer_grammar</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>`ans_image`</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Chiến lược bẫy</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Không phát hiện bẫy rõ — đáp án dựa trên hình ảnh.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>• Hội thoại ngắn giữa 가/나 (2-3 lượt nói), nội dung về hoạt động hàng ngày</t>
-        </is>
-      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
+          <t>• Hội thoại ngắn giữa 가/나 (2-3 lượt nói), nội dung về hoạt động hàng ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t>• Format: 가: 몇 시에 일어납니까?\n나: 여섯 시에 일어납니다.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>• q_answer: ["①", "②", "③", "④"] (310003) hoặc ["1", "2", "3", "4"] (3410006)</t>
-        </is>
-      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>• q_text: rỗng</t>
+          <t>• q_answer: ["①", "②", "③", "④"] (310003) hoặc ["1", "2", "3", "4"] (3410006)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>• q_image: có (4 ảnh mỗi câu)</t>
+          <t>• q_text: rỗng</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
+          <t>• q_image: có (4 ảnh mỗi câu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
           <t>• 4 bức tranh minh họa các cảnh khác nhau → dùng q_image_description để mô tả</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Mỗi bức tranh mô tả một cảnh sinh hoạt. Mô tả bao gồm: ai đang làm gì, ở đâu, chi tiết quan trọng phân biệt các bức.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Quy tắc tạo 4 bức tranh</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>• Bức đúng: khớp chính xác nội dung audio (hành động + bối cảnh + đối tượng)</t>
-        </is>
-      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>• Bức sai 1: đúng bối cảnh nhưng sai hành động</t>
+          <t>• Bức đúng: khớp chính xác nội dung audio (hành động + bối cảnh + đối tượng)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>• Bức sai 2: đúng hành động nhưng sai bối cảnh</t>
+          <t>• Bức sai 1: đúng bối cảnh nhưng sai hành động</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>• Bức sai 2: đúng hành động nhưng sai bối cảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
           <t>• Bức sai 3: khác hoàn toàn nhưng dùng 1 yếu tố gây nhầm lẫn từ audio</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "g_text_audio": "가: 몇 시에 일어납니까?\n나: 여섯 시에 일어납니다.",</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "content": [{</t>
+          <t xml:space="preserve">  "g_text_audio": "가: 몇 시에 일어납니까?\n나: 여섯 시에 일어납니다.",</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_image_description": {</t>
+          <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "1": "남자가 아침 6시에 침대에서 일어나고 있다. 알람시계가 6:00을 가리킨다.",</t>
+          <t xml:space="preserve">    "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "2": "남자가 밤에 침대에 누워 자고 있다. 시계가 10:00을 가리킨다.",</t>
+          <t xml:space="preserve">      "1": "남자가 아침 6시에 침대에서 일어나고 있다. 알람시계가 6:00을 가리킨다.",</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "3": "남자가 아침에 운동을 하고 있다. 공원에서 조깅.",</t>
+          <t xml:space="preserve">      "2": "남자가 밤에 침대에 누워 자고 있다. 시계가 10:00을 가리킨다.",</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "4": "남자가 아침 식사를 하고 있다. 식탁에 앉아 있다."</t>
+          <t xml:space="preserve">      "3": "남자가 아침에 운동을 하고 있다. 공원에서 조깅.",</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">      "4": "남자가 아침 식사를 하고 있다. 식탁에 앉아 있다."</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_answer": ["①", "②", "③", "④"],</t>
+          <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 1</t>
+          <t xml:space="preserve">    "q_answer": ["①", "②", "③", "④"],</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">    "q_correct": 1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>}</t>
         </is>
@@ -6027,6 +5908,7 @@
   <mergeCells count="38">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
@@ -6038,7 +5920,6 @@
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A35:F35"/>
@@ -7718,7 +7599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7940,310 +7821,322 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>answer_grammar</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>`ans_image`</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Chiến lược bẫy</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Bẫy</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>Tỷ lệ</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>`trap_sound_similarity`</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>**LUÔN LUÔN**. 4 đồng hồ hiển thị giờ dễ nhầm lẫn</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>• Một câu đơn nêu thời gian bằng tiếng Hàn</t>
-        </is>
-      </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>• Format: "지금은 열두 시 이십 분입니다."</t>
+          <t>• Một câu đơn nêu thời gian bằng tiếng Hàn</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
+          <t>• Format: "지금은 열두 시 이십 분입니다."</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
           <t>• Dùng dạng formal_polite (~입니다)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>• q_answer: ["1", "2", "3", "4"] — 4 ảnh đồng hồ</t>
-        </is>
-      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>• q_text: rỗng</t>
+          <t>• q_answer: ["1", "2", "3", "4"] — 4 ảnh đồng hồ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>• q_image: có (tất cả 120 câu đều có 4 ảnh đồng hồ)</t>
+          <t>• q_text: rỗng</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>• Đáp án đúng: đồng hồ hiển thị đúng giờ được nói trong audio</t>
+          <t>• q_image: có (tất cả 120 câu đều có 4 ảnh đồng hồ)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
+          <t>• Đáp án đúng: đồng hồ hiển thị đúng giờ được nói trong audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
           <t>• Đáp án sai: 3 đồng hồ hiển thị giờ dễ nhầm</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Mô tả 4 mặt đồng hồ, mỗi mặt hiển thị một giờ khác nhau.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Quy tắc tạo 4 đồng hồ</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>1. 4 đồng hồ PHẢI hiển thị giờ dễ nhầm lẫn với nhau</t>
-        </is>
-      </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>2. Chiến lược gây nhầm:</t>
+          <t>1. 4 đồng hồ PHẢI hiển thị giờ dễ nhầm lẫn với nhau</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>• Đổi giờ/phút (e.g., 12:20 vs 4:12)</t>
+          <t>2. Chiến lược gây nhầm:</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>• Cùng phút khác giờ (e.g., 12:20 vs 2:20)</t>
+          <t>• Đổi giờ/phút (e.g., 12:20 vs 4:12)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>• Cùng giờ khác phút (e.g., 12:20 vs 12:40)</t>
+          <t>• Cùng phút khác giờ (e.g., 12:20 vs 2:20)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>• Đảo kim giờ/kim phút (e.g., 12:20 vs 4:00)</t>
+          <t>• Cùng giờ khác phút (e.g., 12:20 vs 12:40)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
+          <t>• Đảo kim giờ/kim phút (e.g., 12:20 vs 4:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
           <t>3. Ví dụ nhóm: 12:20, 12:40, 2:20, 2:40</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "g_text_audio": "지금은 열두 시 이십 분입니다.",</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "content": [{</t>
+          <t xml:space="preserve">  "g_text_audio": "지금은 열두 시 이십 분입니다.",</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_image_description": {</t>
+          <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "1": "동그란 시계. 긴 바늘이 4, 짧은 바늘이 12를 가리킨다. 12시 20분.",</t>
+          <t xml:space="preserve">    "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "2": "동그란 시계. 긴 바늘이 8, 짧은 바늘이 12를 가리킨다. 12시 40분.",</t>
+          <t xml:space="preserve">      "1": "동그란 시계. 긴 바늘이 4, 짧은 바늘이 12를 가리킨다. 12시 20분.",</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "3": "동그란 시계. 긴 바늘이 4, 짧은 바늘이 2를 가리킨다. 2시 20분.",</t>
+          <t xml:space="preserve">      "2": "동그란 시계. 긴 바늘이 8, 짧은 바늘이 12를 가리킨다. 12시 40분.",</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "4": "동그란 시계. 긴 바늘이 8, 짧은 바늘이 2를 가리킨다. 2시 40분."</t>
+          <t xml:space="preserve">      "3": "동그란 시계. 긴 바늘이 4, 짧은 바늘이 2를 가리킨다. 2시 20분.",</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">      "4": "동그란 시계. 긴 바늘이 8, 짧은 바늘이 2를 가리킨다. 2시 40분."</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_answer": ["1", "2", "3", "4"],</t>
+          <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 1</t>
+          <t xml:space="preserve">    "q_answer": ["1", "2", "3", "4"],</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">    "q_correct": 1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>}</t>
         </is>
@@ -8259,15 +8152,14 @@
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
@@ -8289,6 +8181,7 @@
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>

--- a/kinds_Listen_EPS.xlsx
+++ b/kinds_Listen_EPS.xlsx
@@ -1229,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F262"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2413,659 +2413,644 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="13" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Bóp méo chi tiết nhỏ trong nội dung</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>310002, 310003</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>`trap_action_swap`</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>Bức sai có đúng bối cảnh nhưng sai hành động</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>310003</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>`trap_context_swap`</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>Bức sai có đúng hành động nhưng sai bối cảnh</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>310003</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="13" t="inlineStr">
         <is>
           <t>Quy tắc gán nhãn bẫy</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="11" t="inlineStr">
-        <is>
-          <t>• Mỗi câu hỏi có thể có NHIỀU nhãn bẫy cùng lúc</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t>• Gán nhãn dựa trên ĐÁP ÁN SAI, không phải đáp án đúng</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>• Chỉ gán khi có bằng chứng rõ ràng, không suy đoán</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
+          <t>• Mỗi câu hỏi có thể có NHIỀU nhãn bẫy cùng lúc</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>• Gán nhãn dựa trên ĐÁP ÁN SAI, không phải đáp án đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>• Chỉ gán khi có bằng chứng rõ ràng, không suy đoán</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="9" t="inlineStr">
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="9" t="inlineStr">
         <is>
           <t>Đặc điểm câu hỏi (question_feature)</t>
         </is>
       </c>
-      <c r="B131" s="10" t="n"/>
-      <c r="C131" s="10" t="n"/>
-      <c r="D131" s="10" t="n"/>
-      <c r="E131" s="10" t="n"/>
-      <c r="F131" s="10" t="n"/>
-    </row>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="13" t="inlineStr">
+      <c r="B134" s="10" t="n"/>
+      <c r="C134" s="10" t="n"/>
+      <c r="D134" s="10" t="n"/>
+      <c r="E134" s="10" t="n"/>
+      <c r="F134" s="10" t="n"/>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="13" t="inlineStr">
         <is>
           <t>Nhóm câu hỏi có q_text</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="14" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B133" s="14" t="inlineStr">
+      <c r="B136" s="14" t="inlineStr">
         <is>
           <t>Nhãn tiếng Anh</t>
         </is>
       </c>
-      <c r="C133" s="14" t="inlineStr">
+      <c r="C136" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>`qf_content_match`</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>Content Match</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>"들은 내용으로 맞는 것을 고르십시오"</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>`qf_what`</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>What (General)</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>"무엇입니까?", "무엇을 삽니까?"</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>`qf_what_doing`</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>What Doing</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>"무엇을 하고 있습니까?"</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>`qf_where`</t>
+          <t>`qf_content_match`</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Where/Which</t>
+          <t>Content Match</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>"어디입니까?", "어느 나라?"</t>
+          <t>"들은 내용으로 맞는 것을 고르십시오"</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>`qf_central_thought`</t>
+          <t>`qf_what`</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>Central Thought</t>
+          <t>What (General)</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>"중심 생각으로 맞는 것"</t>
+          <t>"무엇입니까?", "무엇을 삽니까?"</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>`qf_why`</t>
+          <t>`qf_what_doing`</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>Why/Reason</t>
+          <t>What Doing</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>"왜?", "이유"</t>
+          <t>"무엇을 하고 있습니까?"</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>`qf_when_time`</t>
+          <t>`qf_where`</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>When/Time</t>
+          <t>Where/Which</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>"언제?", "몇 시?", "얼마 동안?"</t>
+          <t>"어디입니까?", "어느 나라?"</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>`qf_who`</t>
+          <t>`qf_central_thought`</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>Who</t>
+          <t>Central Thought</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>"누구입니까?"</t>
+          <t>"중심 생각으로 맞는 것"</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>`qf_how_many`</t>
+          <t>`qf_why`</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>How Many</t>
+          <t>Why/Reason</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>"몇 명?", "몇 개?"</t>
+          <t>"왜?", "이유"</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
+          <t>`qf_when_time`</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>When/Time</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>"언제?", "몇 시?", "얼마 동안?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>`qf_who`</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>Who</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>"누구입니까?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>`qf_how_many`</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>How Many</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>"몇 명?", "몇 개?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
           <t>`qf_how_much`</t>
         </is>
       </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>How Much (Price)</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t>"얼마입니까?"</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="13" t="inlineStr">
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="13" t="inlineStr">
         <is>
           <t>Nhóm câu hỏi KHÔNG có q_text</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="14" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B146" s="14" t="inlineStr">
+      <c r="B149" s="14" t="inlineStr">
         <is>
           <t>Kind áp dụng</t>
         </is>
       </c>
-      <c r="C146" s="14" t="inlineStr">
+      <c r="C149" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="6" t="inlineStr">
-        <is>
-          <t>`qf_direct_qa`</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>310004</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>Nghe câu hỏi -&gt; chọn câu trả lời trực tiếp</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>`qf_next_utterance`</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>3410005</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>Nghe hội thoại -&gt; chọn câu nối tiếp</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>`qf_match_image`</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>310003</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>Nghe -&gt; chọn hình khớp</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>`qf_match_content`</t>
+          <t>`qf_direct_qa`</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>310005</t>
+          <t>310004</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>Nghe -&gt; chọn phát biểu khớp nội dung</t>
+          <t>Nghe câu hỏi -&gt; chọn câu trả lời trực tiếp</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>`qf_identify_sound`</t>
+          <t>`qf_next_utterance`</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>310001</t>
+          <t>3410005</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>Nghe -&gt; nhận diện từ/câu</t>
+          <t>Nghe hội thoại -&gt; chọn câu nối tiếp</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>`qf_identify_time`</t>
+          <t>`qf_match_image`</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>3410002</t>
+          <t>310003</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>Nghe giờ -&gt; chọn đồng hồ</t>
+          <t>Nghe -&gt; chọn hình khớp</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>`qf_image_qa`</t>
+          <t>`qf_match_content`</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>310002</t>
+          <t>310005</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>Nhìn hình + nghe 4 câu mô tả -&gt; chọn đúng</t>
+          <t>Nghe -&gt; chọn phát biểu khớp nội dung</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
+          <t>`qf_identify_sound`</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>310001</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>Nghe -&gt; nhận diện từ/câu</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>`qf_identify_time`</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>3410002</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>Nghe giờ -&gt; chọn đồng hồ</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>`qf_image_qa`</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>310002</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>Nhìn hình + nghe 4 câu mô tả -&gt; chọn đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
           <t>`qf_multi_comprehension`</t>
         </is>
       </c>
-      <c r="B154" s="6" t="inlineStr">
+      <c r="B157" s="6" t="inlineStr">
         <is>
           <t>310006</t>
         </is>
       </c>
-      <c r="C154" s="6" t="inlineStr">
+      <c r="C157" s="6" t="inlineStr">
         <is>
           <t>Nghe dài và trả lời 2 câu hỏi</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc ngữ pháp trong audio (grammar_semantic)</t>
-        </is>
-      </c>
-      <c r="B157" s="10" t="n"/>
-      <c r="C157" s="10" t="n"/>
-      <c r="D157" s="10" t="n"/>
-      <c r="E157" s="10" t="n"/>
-      <c r="F157" s="10" t="n"/>
-    </row>
-    <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="13" t="inlineStr">
-        <is>
-          <t>Phân bố Level 3 (2.242 câu, chỉ liệt kê &gt;=5%)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc ngữ pháp trong audio (grammar_semantic)</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="n"/>
+      <c r="C160" s="10" t="n"/>
+      <c r="D160" s="10" t="n"/>
+      <c r="E160" s="10" t="n"/>
+      <c r="F160" s="10" t="n"/>
+    </row>
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="13" t="inlineStr">
+        <is>
+          <t>Phân bố Level 3 (2.242 câu, chỉ liệt kê &gt;=5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
           <t>gram_honorific_시(21%), gram_request_세요(19%), gram_honorific_습니다(18%), gram_cause_니까(8%), gram_cond_면(7%), gram_contrast_는데(7%), gram_prog_고있(6%), gram_intent_겠(6%), gram_cause_어서(5%)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="22" customHeight="1">
-      <c r="A160" s="13" t="inlineStr">
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="13" t="inlineStr">
         <is>
           <t>Bảng nhãn ngữ pháp theo ý nghĩa (Level 3)</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="14" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B161" s="14" t="inlineStr">
+      <c r="B164" s="14" t="inlineStr">
         <is>
           <t>Cấu trúc</t>
         </is>
       </c>
-      <c r="C161" s="14" t="inlineStr">
+      <c r="C164" s="14" t="inlineStr">
         <is>
           <t>Ý nghĩa</t>
         </is>
       </c>
-      <c r="D161" s="14" t="inlineStr">
+      <c r="D164" s="14" t="inlineStr">
         <is>
           <t>L3</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>`gram_cause_어서`</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>~어서/아서</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>Nguyên nhân (nhẹ)</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>`gram_cause_니까`</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>~니까</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>Nguyên nhân (nhấn mạnh)</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="6" t="inlineStr">
-        <is>
-          <t>`gram_cond_면`</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>~(으)면</t>
-        </is>
-      </c>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>Điều kiện</t>
-        </is>
-      </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>7%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>`gram_contrast_지만`</t>
+          <t>`gram_cause_어서`</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>~지만</t>
+          <t>~어서/아서</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>Đối lập trực tiếp</t>
+          <t>Nguyên nhân (nhẹ)</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>`gram_contrast_는데`</t>
+          <t>`gram_cause_니까`</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>~는데/은데</t>
+          <t>~니까</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>Bối cảnh/đối lập mềm</t>
+          <t>Nguyên nhân (nhấn mạnh)</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>8%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>`gram_intent_려고`</t>
+          <t>`gram_cond_면`</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>~(으)려고</t>
+          <t>~(으)면</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>Ý định</t>
+          <t>Điều kiện</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>`gram_intent_겠`</t>
+          <t>`gram_contrast_지만`</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>~겠어요/겠습니다</t>
+          <t>~지만</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>Dự định/suy đoán</t>
+          <t>Đối lập trực tiếp</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>3%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>`gram_request_세요`</t>
+          <t>`gram_contrast_는데`</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>~(으)세요</t>
+          <t>~는데/은데</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>Yêu cầu lịch sự</t>
+          <t>Bối cảnh/đối lập mềm</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>7%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>`gram_request_주세요`</t>
+          <t>`gram_intent_려고`</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>~주세요</t>
+          <t>~(으)려고</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>Nhờ vả cụ thể</t>
+          <t>Ý định</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
@@ -3077,17 +3062,17 @@
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>`gram_prog_고있`</t>
+          <t>`gram_intent_겠`</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>~고 있다</t>
+          <t>~겠어요/겠습니다</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>Đang diễn ra</t>
+          <t>Dự định/suy đoán</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
@@ -3099,891 +3084,940 @@
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>`gram_honorific_시`</t>
+          <t>`gram_request_세요`</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>~시/셨/세요</t>
+          <t>~(으)세요</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>Kính ngữ (시)</t>
+          <t>Yêu cầu lịch sự</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
+          <t>`gram_request_주세요`</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>~주세요</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>Nhờ vả cụ thể</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>`gram_prog_고있`</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>~고 있다</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>Đang diễn ra</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>`gram_honorific_시`</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>~시/셨/세요</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>Kính ngữ (시)</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
           <t>`gram_honorific_습니다`</t>
         </is>
       </c>
-      <c r="B173" s="6" t="inlineStr">
+      <c r="B176" s="6" t="inlineStr">
         <is>
           <t>~습니다/ㅂ니다</t>
         </is>
       </c>
-      <c r="C173" s="6" t="inlineStr">
+      <c r="C176" s="6" t="inlineStr">
         <is>
           <t>Kính ngữ trang trọng</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D176" s="6" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="22" customHeight="1">
-      <c r="A175" s="13" t="inlineStr">
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="13" t="inlineStr">
         <is>
           <t>Ngữ pháp trong đáp án (answer_grammar)</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="14" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B176" s="14" t="inlineStr">
+      <c r="B179" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="C176" s="14" t="inlineStr">
+      <c r="C179" s="14" t="inlineStr">
         <is>
           <t>Kind áp dụng</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>`ans_word_phrase`</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án là từ đơn / cụm ngắn</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>310001</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>`ans_formal_polite`</t>
-        </is>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án dùng ~ㅂ니다/습니다</t>
-        </is>
-      </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>310002</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="6" t="inlineStr">
-        <is>
-          <t>`ans_image`</t>
-        </is>
-      </c>
-      <c r="B179" s="6" t="inlineStr">
-        <is>
-          <t>Đáp án là hình ảnh</t>
-        </is>
-      </c>
-      <c r="C179" s="6" t="inlineStr">
-        <is>
-          <t>310003, 3410002</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>`ans_formal`</t>
+          <t>`ans_word_phrase`</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>Đáp án dùng ~ㅂ니다</t>
+          <t>Đáp án là từ đơn / cụm ngắn</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>310004, 310005, 310006</t>
+          <t>310001</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
+          <t>`ans_formal_polite`</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án dùng ~ㅂ니다/습니다</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>310002</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>`ans_image`</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án là hình ảnh</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>310003, 3410002</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>`ans_formal`</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án dùng ~ㅂ니다</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>310004, 310005, 310006</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
           <t>`ans_informal_polite`</t>
         </is>
       </c>
-      <c r="B181" s="6" t="inlineStr">
+      <c r="B184" s="6" t="inlineStr">
         <is>
           <t>Đáp án dùng ~아/어요</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr">
+      <c r="C184" s="6" t="inlineStr">
         <is>
           <t>3410005</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="11" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="9" t="inlineStr">
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio (audio_format)</t>
         </is>
       </c>
-      <c r="B184" s="10" t="n"/>
-      <c r="C184" s="10" t="n"/>
-      <c r="D184" s="10" t="n"/>
-      <c r="E184" s="10" t="n"/>
-      <c r="F184" s="10" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="14" t="inlineStr">
+      <c r="B187" s="10" t="n"/>
+      <c r="C187" s="10" t="n"/>
+      <c r="D187" s="10" t="n"/>
+      <c r="E187" s="10" t="n"/>
+      <c r="F187" s="10" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B185" s="14" t="inlineStr">
+      <c r="B188" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="C185" s="14" t="inlineStr">
+      <c r="C188" s="14" t="inlineStr">
         <is>
           <t>Kind chính</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>`audio_dialog_가나`</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
-        <is>
-          <t>Hội thoại 가/나 (EPS)</t>
-        </is>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>310003-310006</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>`audio_single_word`</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
-        <is>
-          <t>Từ đơn/cụm ngắn (&lt;15 ký tự)</t>
-        </is>
-      </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>310001, 3410002</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>`audio_single_sentence`</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>Câu đơn (15-50 ký tự)</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>310004, 3410005</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
+          <t>`audio_dialog_가나`</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>Hội thoại 가/나 (EPS)</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>310003-310006</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>`audio_single_word`</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>Từ đơn/cụm ngắn (&lt;15 ký tự)</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>310001, 3410002</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>`audio_single_sentence`</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>Câu đơn (15-50 ký tự)</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>310004, 3410005</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
           <t>`audio_numbered`</t>
         </is>
       </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="B192" s="6" t="inlineStr">
         <is>
           <t>4 câu mô tả đánh số (1. 2. 3. 4.)</t>
         </is>
       </c>
-      <c r="C189" s="6" t="inlineStr">
+      <c r="C192" s="6" t="inlineStr">
         <is>
           <t>310002</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="11" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="9" t="inlineStr">
+    <row r="195" ht="22" customHeight="1">
+      <c r="A195" s="9" t="inlineStr">
         <is>
           <t>Thang đo khó (Difficulty Scale) — EPS kinds only</t>
         </is>
       </c>
-      <c r="B192" s="10" t="n"/>
-      <c r="C192" s="10" t="n"/>
-      <c r="D192" s="10" t="n"/>
-      <c r="E192" s="10" t="n"/>
-      <c r="F192" s="10" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="14" t="inlineStr">
+      <c r="B195" s="10" t="n"/>
+      <c r="C195" s="10" t="n"/>
+      <c r="D195" s="10" t="n"/>
+      <c r="E195" s="10" t="n"/>
+      <c r="F195" s="10" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="14" t="inlineStr">
         <is>
           <t>Mức</t>
         </is>
       </c>
-      <c r="B193" s="14" t="inlineStr">
+      <c r="B196" s="14" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C193" s="14" t="inlineStr">
+      <c r="C196" s="14" t="inlineStr">
         <is>
           <t>Kiểu suy luận</t>
         </is>
       </c>
-      <c r="D193" s="14" t="inlineStr">
+      <c r="D196" s="14" t="inlineStr">
         <is>
           <t>Nhãn</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
-        <is>
-          <t>310001, 3410002</t>
-        </is>
-      </c>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>`sound_recognition` / `time_recognition`</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr">
-        <is>
-          <t>Nhận diện từ/giờ</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B195" s="6" t="inlineStr">
-        <is>
-          <t>310004, 310002</t>
-        </is>
-      </c>
-      <c r="C195" s="6" t="inlineStr">
-        <is>
-          <t>`direct_match` / `image_qa`</t>
-        </is>
-      </c>
-      <c r="D195" s="6" t="inlineStr">
-        <is>
-          <t>Hỏi-đáp đơn giản</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
-        <is>
-          <t>3410005</t>
-        </is>
-      </c>
-      <c r="C196" s="6" t="inlineStr">
-        <is>
-          <t>`pragmatic_response`</t>
-        </is>
-      </c>
-      <c r="D196" s="6" t="inlineStr">
-        <is>
-          <t>Chọn câu nối tiếp</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>310003</t>
+          <t>310001, 3410002</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>`scene_matching`</t>
+          <t>`sound_recognition` / `time_recognition`</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>Chọn hình liên quan</t>
+          <t>Nhận diện từ/giờ</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>310005</t>
+          <t>310004, 310002</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>`detail_extraction`</t>
+          <t>`direct_match` / `image_qa`</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Trích xuất chi tiết</t>
+          <t>Hỏi-đáp đơn giản</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>3410005</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>`pragmatic_response`</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>Chọn câu nối tiếp</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>310003</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>`scene_matching`</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>Chọn hình liên quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>310005</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>`detail_extraction`</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>Trích xuất chi tiết</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B199" s="6" t="inlineStr">
+      <c r="B202" s="6" t="inlineStr">
         <is>
           <t>310006</t>
         </is>
       </c>
-      <c r="C199" s="6" t="inlineStr">
+      <c r="C202" s="6" t="inlineStr">
         <is>
           <t>`multi_comprehension`</t>
         </is>
       </c>
-      <c r="D199" s="6" t="inlineStr">
+      <c r="D202" s="6" t="inlineStr">
         <is>
           <t>2 câu hỏi / đoạn dài</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="22" customHeight="1">
-      <c r="A201" s="13" t="inlineStr">
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="13" t="inlineStr">
         <is>
           <t>Mô tả kiểu suy luận (reasoning_type)</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="14" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B202" s="14" t="inlineStr">
+      <c r="B205" s="14" t="inlineStr">
         <is>
           <t>Mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="6" t="inlineStr">
-        <is>
-          <t>`sound_recognition`</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>Nhận diện chính xác từ/câu được nghe</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="6" t="inlineStr">
-        <is>
-          <t>`time_recognition`</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>Nghe giờ, chọn đồng hồ phù hợp</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="6" t="inlineStr">
-        <is>
-          <t>`direct_match`</t>
-        </is>
-      </c>
-      <c r="B205" s="6" t="inlineStr">
-        <is>
-          <t>Ghép câu hỏi với câu trả lời trực tiếp</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>`image_qa`</t>
+          <t>`sound_recognition`</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>Nhìn hình, nghe câu hỏi + đáp án, chọn đúng</t>
+          <t>Nhận diện chính xác từ/câu được nghe</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>`pragmatic_response`</t>
+          <t>`time_recognition`</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>Chọn phản hồi phù hợp ngữ cảnh giao tiếp</t>
+          <t>Nghe giờ, chọn đồng hồ phù hợp</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>`scene_matching`</t>
+          <t>`direct_match`</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>Nghe audio, chọn bức tranh minh họa khớp</t>
+          <t>Ghép câu hỏi với câu trả lời trực tiếp</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>`detail_extraction`</t>
+          <t>`image_qa`</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>Trích xuất chi tiết cụ thể từ hội thoại</t>
+          <t>Nhìn hình, nghe câu hỏi + đáp án, chọn đúng</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
+          <t>`pragmatic_response`</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>Chọn phản hồi phù hợp ngữ cảnh giao tiếp</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>`scene_matching`</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>Nghe audio, chọn bức tranh minh họa khớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>`detail_extraction`</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>Trích xuất chi tiết cụ thể từ hội thoại</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
           <t>`multi_comprehension`</t>
         </is>
       </c>
-      <c r="B210" s="6" t="inlineStr">
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>Trả lời 2 câu hỏi từ 1 đoạn</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="11" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="11" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="22" customHeight="1">
-      <c r="A213" s="9" t="inlineStr">
+    <row r="216" ht="22" customHeight="1">
+      <c r="A216" s="9" t="inlineStr">
         <is>
           <t>Cấp độ giao tiếp trong audio (speech_level)</t>
         </is>
       </c>
-      <c r="B213" s="10" t="n"/>
-      <c r="C213" s="10" t="n"/>
-      <c r="D213" s="10" t="n"/>
-      <c r="E213" s="10" t="n"/>
-      <c r="F213" s="10" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="14" t="inlineStr">
+      <c r="B216" s="10" t="n"/>
+      <c r="C216" s="10" t="n"/>
+      <c r="D216" s="10" t="n"/>
+      <c r="E216" s="10" t="n"/>
+      <c r="F216" s="10" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="14" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B214" s="14" t="inlineStr">
+      <c r="B217" s="14" t="inlineStr">
         <is>
           <t>Audio chính</t>
         </is>
       </c>
-      <c r="C214" s="14" t="inlineStr">
+      <c r="C217" s="14" t="inlineStr">
         <is>
           <t>Đáp án</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="6" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="B218" s="6" t="inlineStr">
         <is>
           <t>`informal_polite` 37%, `modifier` 31%, `connective` 16%</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
+      <c r="C218" s="6" t="inlineStr">
         <is>
           <t>`formal_polite` (~ㅂ니다) cho EPS</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="11" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="11" t="inlineStr">
         <is>
           <t>Quy tắc: Audio EPS dùng informal_polite là chính. Đáp án EPS thường dùng formal_polite (~ㅂ니다) — xem answer_grammar ans_formal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="11" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="22" customHeight="1">
-      <c r="A219" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc chung khi gen câu hỏi</t>
-        </is>
-      </c>
-      <c r="B219" s="10" t="n"/>
-      <c r="C219" s="10" t="n"/>
-      <c r="D219" s="10" t="n"/>
-      <c r="E219" s="10" t="n"/>
-      <c r="F219" s="10" t="n"/>
-    </row>
-    <row r="220" ht="22" customHeight="1">
-      <c r="A220" s="13" t="inlineStr">
-        <is>
-          <t>1. Chất lượng nội dung tiếng Hàn</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t>• Dùng ngữ pháp đúng Level 3 (xem bảng speech_level + grammar_semantic)</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="11" t="inlineStr">
-        <is>
-          <t>• Hội thoại tự nhiên, đa dạng chủ đề đời sống + lao động</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="11" t="inlineStr">
-        <is>
-          <t>• KHÔNG lặp lại từ vựng/ngữ cảnh giữa các câu trong cùng batch</t>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="22" customHeight="1">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc chung khi gen câu hỏi</t>
+        </is>
+      </c>
+      <c r="B222" s="10" t="n"/>
+      <c r="C222" s="10" t="n"/>
+      <c r="D222" s="10" t="n"/>
+      <c r="E222" s="10" t="n"/>
+      <c r="F222" s="10" t="n"/>
+    </row>
+    <row r="223" ht="22" customHeight="1">
+      <c r="A223" s="13" t="inlineStr">
+        <is>
+          <t>1. Chất lượng nội dung tiếng Hàn</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t>• Pha trộn chủ đề chung + chủ đề EPS đặc thù</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="22" customHeight="1">
-      <c r="A225" s="13" t="inlineStr">
-        <is>
-          <t>2. Xây dựng đáp án sai (distractor)</t>
+          <t>• Dùng ngữ pháp đúng Level 3 (xem bảng speech_level + grammar_semantic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="11" t="inlineStr">
+        <is>
+          <t>• Hội thoại tự nhiên, đa dạng chủ đề đời sống + lao động</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t>• Tuân theo tỷ lệ bẫy của từng kind (xem file kind tương ứng)</t>
+          <t>• KHÔNG lặp lại từ vựng/ngữ cảnh giữa các câu trong cùng batch</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t>• Phải hợp lý nhưng SAI về nội dung</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="11" t="inlineStr">
-        <is>
-          <t>• Tái sử dụng từ vựng audio khi kind yêu cầu shared_word</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="22" customHeight="1">
-      <c r="A229" s="13" t="inlineStr">
-        <is>
-          <t>3. Giải thích (explain)</t>
+          <t>• Pha trộn chủ đề chung + chủ đề EPS đặc thù</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="22" customHeight="1">
+      <c r="A228" s="13" t="inlineStr">
+        <is>
+          <t>2. Xây dựng đáp án sai (distractor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t>• Tuân theo tỷ lệ bẫy của từng kind (xem file kind tương ứng)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t>• vi: Dịch cả 4 đáp án -&gt; dấu -------------------- -&gt; giải thích đáp án đúng, ghi chú trap type cho từng đáp án sai</t>
+          <t>• Phải hợp lý nhưng SAI về nội dung</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t>• en: Tương tự bằng tiếng Anh</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="11" t="inlineStr">
-        <is>
-          <t>• Highlight từ vựng/ngữ pháp quan trọng</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="22" customHeight="1">
-      <c r="A233" s="13" t="inlineStr">
-        <is>
-          <t>4. Số lượng</t>
+          <t>• Tái sử dụng từ vựng audio khi kind yêu cầu shared_word</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="22" customHeight="1">
+      <c r="A232" s="13" t="inlineStr">
+        <is>
+          <t>3. Giải thích (explain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
+          <t>• vi: Dịch cả 4 đáp án -&gt; dấu -------------------- -&gt; giải thích đáp án đúng, ghi chú trap type cho từng đáp án sai</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t>• Mặc định: 5 câu mỗi kind nếu user không chỉ định</t>
+          <t>• en: Tương tự bằng tiếng Anh</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t>• Tối đa: 20 câu mỗi lần</t>
+          <t>• Highlight từ vựng/ngữ pháp quan trọng</t>
         </is>
       </c>
     </row>
     <row r="236" ht="22" customHeight="1">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>5. Kiểm tra sau khi gen (Validation Checklist)</t>
+          <t>4. Số lượng</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t>• [ ] q_correct nằm trong 1-4</t>
+          <t>• Mặc định: 5 câu mỗi kind nếu user không chỉ định</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t>• [ ] 4 đáp án không trùng nhau</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="11" t="inlineStr">
-        <is>
-          <t>• [ ] Audio là tiếng Hàn tự nhiên</t>
+          <t>• Tối đa: 20 câu mỗi lần</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="22" customHeight="1">
+      <c r="A239" s="13" t="inlineStr">
+        <is>
+          <t>5. Kiểm tra sau khi gen (Validation Checklist)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Ngữ pháp đúng Level 3</t>
+          <t>• [ ] q_correct nằm trong 1-4</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Bẫy đúng phân bố của kind</t>
+          <t>• [ ] 4 đáp án không trùng nhau</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="11" t="inlineStr">
         <is>
-          <t>• [ ] Bản dịch (vi/en) chính xác</t>
+          <t>• [ ] Audio là tiếng Hàn tự nhiên</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="11" t="inlineStr">
         <is>
-          <t>• [ ] explain chứa dịch 4 đáp án + lý do đáp án đúng + trap type cho đáp án sai</t>
+          <t>• [ ] Ngữ pháp đúng Level 3</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t>• [ ] count_question khớp số phần tử trong content</t>
+          <t>• [ ] Bẫy đúng phân bố của kind</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t>• [ ] level luôn = 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="22" customHeight="1">
-      <c r="A246" s="9" t="inlineStr">
-        <is>
-          <t>Workflow</t>
-        </is>
-      </c>
-      <c r="B246" s="10" t="n"/>
-      <c r="C246" s="10" t="n"/>
-      <c r="D246" s="10" t="n"/>
-      <c r="E246" s="10" t="n"/>
-      <c r="F246" s="10" t="n"/>
+          <t>• [ ] Bản dịch (vi/en) chính xác</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="11" t="inlineStr">
+        <is>
+          <t>• [ ] explain chứa dịch 4 đáp án + lý do đáp án đúng + trap type cho đáp án sai</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t>1. User chỉ định kind -&gt; đọc file kinds/{kind}.md</t>
+          <t>• [ ] count_question khớp số phần tử trong content</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t>2. Hỏi số lượng (mặc định 5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="11" t="inlineStr">
-        <is>
-          <t>3. Gen câu hỏi theo JSON format + quy tắc kind + chiến lược bẫy</t>
-        </is>
-      </c>
+          <t>• [ ] level luôn = 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="22" customHeight="1">
+      <c r="A249" s="9" t="inlineStr">
+        <is>
+          <t>Workflow</t>
+        </is>
+      </c>
+      <c r="B249" s="10" t="n"/>
+      <c r="C249" s="10" t="n"/>
+      <c r="D249" s="10" t="n"/>
+      <c r="E249" s="10" t="n"/>
+      <c r="F249" s="10" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="11" t="inlineStr">
         <is>
-          <t>4. Lưu JSON tạm -&gt; chạy scripts/save_listen.py để tách CSV theo kind</t>
+          <t>1. User chỉ định kind -&gt; đọc file kinds/{kind}.md</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
         <is>
+          <t>2. Hỏi số lượng (mặc định 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="11" t="inlineStr">
+        <is>
+          <t>3. Gen câu hỏi theo JSON format + quy tắc kind + chiến lược bẫy</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>4. Lưu JSON tạm -&gt; chạy scripts/save_listen.py để tách CSV theo kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="11" t="inlineStr">
+        <is>
           <t>5. Validate theo checklist</t>
         </is>
       </c>
     </row>
-    <row r="252" ht="22" customHeight="1">
-      <c r="A252" s="13" t="inlineStr">
+    <row r="255" ht="22" customHeight="1">
+      <c r="A255" s="13" t="inlineStr">
         <is>
           <t>Lưu kết quả bằng script</t>
         </is>
       </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="12" t="inlineStr">
-        <is>
-          <t># Lưu CSV theo kind + JSON + merge tổng</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="12" t="inlineStr">
-        <is>
-          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py gen_temp.json -o output/listen-eps --json --merge</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="12" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="12" t="inlineStr">
         <is>
-          <t># Chỉ validate</t>
+          <t># Lưu CSV theo kind + JSON + merge tổng</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="12" t="inlineStr">
         <is>
-          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py gen_temp.json --validate-only</t>
+          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py gen_temp.json -o output/listen-eps --json --merge</t>
         </is>
       </c>
     </row>
@@ -3993,19 +4027,36 @@
     <row r="259">
       <c r="A259" s="12" t="inlineStr">
         <is>
-          <t># Append thêm batch mới</t>
+          <t># Chỉ validate</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="12" t="inlineStr">
         <is>
+          <t>python skills/topik-listen-gen-eps/scripts/save_listen.py gen_temp.json --validate-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="12" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="12" t="inlineStr">
+        <is>
+          <t># Append thêm batch mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="12" t="inlineStr">
+        <is>
           <t>python skills/topik-listen-gen-eps/scripts/save_listen.py new_batch.json --append</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="11" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="11" t="inlineStr">
         <is>
           <t>Output: output/listen-eps/level_3/{kind}.csv</t>
         </is>
@@ -4013,12 +4064,11 @@
     </row>
   </sheetData>
   <mergeCells count="158">
-    <mergeCell ref="A183:F183"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A118:F118"/>
     <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A133:F133"/>
     <mergeCell ref="A238:F238"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
@@ -4027,15 +4077,18 @@
     <mergeCell ref="A239:F239"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A160:F160"/>
-    <mergeCell ref="A175:F175"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A263:F263"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A159:F159"/>
     <mergeCell ref="A224:F224"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A134:F134"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A161:F161"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A249:F249"/>
@@ -4045,6 +4098,7 @@
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A186:F186"/>
     <mergeCell ref="A257:F257"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A226:F226"/>
@@ -4059,48 +4113,48 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A212:F212"/>
     <mergeCell ref="A243:F243"/>
+    <mergeCell ref="A252:F252"/>
     <mergeCell ref="A221:F221"/>
-    <mergeCell ref="A252:F252"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A236:F236"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A163:F163"/>
     <mergeCell ref="A223:F223"/>
+    <mergeCell ref="A195:F195"/>
     <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A204:F204"/>
     <mergeCell ref="A85:F85"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A213:F213"/>
-    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A259:F259"/>
     <mergeCell ref="A254:F254"/>
-    <mergeCell ref="A259:F259"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A135:F135"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A262:F262"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A240:F240"/>
+    <mergeCell ref="A215:F215"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A230:F230"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A127:F127"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A232:F232"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A216:F216"/>
     <mergeCell ref="A225:F225"/>
+    <mergeCell ref="A178:F178"/>
     <mergeCell ref="A79:F79"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A218:F218"/>
+    <mergeCell ref="A162:F162"/>
     <mergeCell ref="A227:F227"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A217:F217"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A129:F129"/>
@@ -4125,7 +4179,6 @@
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A245:F245"/>
     <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A157:F157"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A36:F36"/>
@@ -4137,7 +4190,6 @@
     <mergeCell ref="A87:F87"/>
     <mergeCell ref="A65:F65"/>
     <mergeCell ref="A246:F246"/>
-    <mergeCell ref="A128:F128"/>
     <mergeCell ref="A255:F255"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
@@ -4145,30 +4197,29 @@
     <mergeCell ref="A89:F89"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A192:F192"/>
     <mergeCell ref="A248:F248"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A235:F235"/>
     <mergeCell ref="A247:F247"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A219:F219"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A194:F194"/>
     <mergeCell ref="A234:F234"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A184:F184"/>
     <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A156:F156"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A67:F67"/>
     <mergeCell ref="A220:F220"/>
     <mergeCell ref="A130:F130"/>
     <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A201:F201"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A261:F261"/>
     <mergeCell ref="A222:F222"/>
     <mergeCell ref="A132:F132"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A187:F187"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
@@ -4716,7 +4767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4970,315 +5021,343 @@
       <c r="F24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Không phát hiện bẫy rõ — đáp án nằm trong audio, không phải text options.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Mô tả đúng bối cảnh nhưng sai chi tiết hành động</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>`trap_shared_noun`</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án dùng lại từ vựng trong audio nhưng sai nội dung</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>`trap_neg_없안`</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Đáp án đảo nghĩa so với nội dung audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>• 4 câu mô tả được đọc to (đánh số 1-4), mô tả điều có thể đang xảy ra trong hình</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>• Format:</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. 식사를 하고 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. 빨래를 하고 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. 머리를 자르고 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. 김치를 만들고 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc đáp án</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>• q_answer: ["1. ", "2. ", "3. ", "4. "] (310002) hoặc ["1.", "2.", "3.", "4."] (3410003) — đáp án nằm trong audio</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>• q_text: có câu hỏi về hình (e.g., "사람들이 무엇을 하고 있습니까?")</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>• q_image: có (1 ảnh mỗi câu)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>Phân loại q_text (8 dạng)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Dạng</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>Số câu</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>Ví dụ</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>`object_what`</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>이것은 무엇입니까?</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>`action_doing`</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>이 사람은 무엇을 하고 있습니까?</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>`place_where`</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>여기는 어디입니까?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>`date_when`</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>언제입니까?</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>`object_job`</t>
+          <t>`object_what`</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>이 사람의 직업은 무엇입니까?</t>
+          <t>이것은 무엇입니까?</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>`weather`</t>
+          <t>`action_doing`</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>날씨가 어떻습니까?</t>
+          <t>이 사람은 무엇을 하고 있습니까?</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>`count`</t>
+          <t>`place_where`</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>몇 개입니까?</t>
+          <t>여기는 어디입니까?</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>`date_when`</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>언제입니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>`object_job`</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>이 사람의 직업은 무엇입니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>`weather`</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>날씨가 어떻습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>`count`</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>몇 개입니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
           <t>`quality`</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>어떤 것입니까?</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Cách mô tả ảnh (q_image_description)</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Mỗi câu có 1 bức tranh. Dùng key "image" để mô tả cảnh trong hình.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc tạo audio và hình</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="10" t="n"/>
-      <c r="E51" s="10" t="n"/>
-      <c r="F51" s="10" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>1. Hình phải mô tả cảnh rõ ràng, dễ nhận biết</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>2. Audio gồm 1 câu đúng + 3 câu hợp lý nhưng sai so với hình</t>
-        </is>
-      </c>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>3. 3 câu sai phải liên quan đến cùng chủ đề nhưng khác hành động/đối tượng/địa điểm</t>
+          <t>Mỗi câu có 1 bức tranh. Dùng key "image" để mô tả cảnh trong hình.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>Ví dụ</t>
+          <t>Quy tắc tạo audio và hình</t>
         </is>
       </c>
       <c r="B55" s="10" t="n"/>
@@ -5288,96 +5367,128 @@
       <c r="F55" s="10" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>1. Hình phải mô tả cảnh rõ ràng, dễ nhận biết</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "g_text_audio": "1. 식사를 하고 있습니다.\n2. 빨래를 하고 있습니다.\n3. 머리를 자르고 있습니다.\n4. 김치를 만들고 있습니다.",</t>
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>2. Audio gồm 1 câu đúng + 3 câu hợp lý nhưng sai so với hình</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "content": [{</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_text": "사람들이 무엇을 하고 있습니까?",</t>
-        </is>
-      </c>
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>3. 3 câu sai phải liên quan đến cùng chủ đề nhưng khác hành động/đối tượng/địa điểm</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Ví dụ</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_image_description": {</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "image": "여자가 부엌에서 빨래를 하고 있다. 세탁기 옆에 빨래 바구니가 있다."</t>
+          <t xml:space="preserve">  "g_text_audio": "1. 식사를 하고 있습니다.\n2. 빨래를 하고 있습니다.\n3. 머리를 자르고 있습니다.\n4. 김치를 만들고 있습니다.",</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_answer": ["1. ", "2. ", "3. ", "4. "],</t>
+          <t xml:space="preserve">    "q_text": "사람들이 무엇을 하고 있습니까?",</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 2</t>
+          <t xml:space="preserve">    "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">      "image": "여자가 부엌에서 빨래를 하고 있다. 세탁기 옆에 빨래 바구니가 있다."</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_answer": ["1. ", "2. ", "3. ", "4. "],</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_correct": 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="38">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A17:F17"/>
@@ -5385,26 +5496,26 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A67:F67"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A70:F70"/>
     <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A65:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5416,7 +5527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5670,252 +5781,314 @@
       <c r="F24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Không phát hiện bẫy rõ — đáp án dựa trên hình ảnh.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Bẫy</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Tỷ lệ</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>`trap_action_swap`</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Bức sai có đúng bối cảnh nhưng sai hành động</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>`trap_context_swap`</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Bức sai có đúng hành động nhưng sai bối cảnh/nơi chốn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>`trap_detail_distort`</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Bức sai đúng tổng thể nhưng sai chi tiết nhỏ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Cấu trúc audio</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>• Hội thoại ngắn giữa 가/나 (2-3 lượt nói), nội dung về hoạt động hàng ngày</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>• Format: 가: 몇 시에 일어납니까?\n나: 여섯 시에 일어납니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Cấu trúc đáp án</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>• q_answer: ["①", "②", "③", "④"] (310003) hoặc ["1", "2", "3", "4"] (3410006)</t>
-        </is>
-      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>• q_text: rỗng</t>
+          <t>• Hội thoại ngắn giữa 가/나 (2-3 lượt nói), nội dung về hoạt động hàng ngày</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>• q_image: có (4 ảnh mỗi câu)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>• 4 bức tranh minh họa các cảnh khác nhau → dùng q_image_description để mô tả</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Cách mô tả ảnh (q_image_description)</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
+          <t>• Format: 가: 몇 시에 일어납니까?\n나: 여섯 시에 일어납니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Cấu trúc đáp án</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>• q_answer: ["①", "②", "③", "④"] (310003) hoặc ["1", "2", "3", "4"] (3410006)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Mỗi bức tranh mô tả một cảnh sinh hoạt. Mô tả bao gồm: ai đang làm gì, ở đâu, chi tiết quan trọng phân biệt các bức.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Quy tắc tạo 4 bức tranh</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
+          <t>• q_text: rỗng</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>• q_image: có (4 ảnh mỗi câu)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>• Bức đúng: khớp chính xác nội dung audio (hành động + bối cảnh + đối tượng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>• Bức sai 1: đúng bối cảnh nhưng sai hành động</t>
-        </is>
-      </c>
+          <t>• 4 bức tranh minh họa các cảnh khác nhau → dùng q_image_description để mô tả</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Cách mô tả ảnh (q_image_description)</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>Mỗi bức tranh mô tả một cảnh sinh hoạt. Mô tả bao gồm: ai đang làm gì, ở đâu, chi tiết quan trọng phân biệt các bức.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Quy tắc tạo 4 bức tranh</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>• Bức đúng: khớp chính xác nội dung audio (hành động + bối cảnh + đối tượng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>• Bức sai 1: đúng bối cảnh nhưng sai hành động</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
           <t>• Bức sai 2: đúng hành động nhưng sai bối cảnh</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>• Bức sai 3: khác hoàn toàn nhưng dùng 1 yếu tố gây nhầm lẫn từ audio</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Ví dụ</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>{</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "g_text_audio": "가: 몇 시에 일어납니까?\n나: 여섯 시에 일어납니다.",</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "content": [{</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "q_image_description": {</t>
-        </is>
-      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "1": "남자가 아침 6시에 침대에서 일어나고 있다. 알람시계가 6:00을 가리킨다.",</t>
+          <t>{</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "2": "남자가 밤에 침대에 누워 자고 있다. 시계가 10:00을 가리킨다.",</t>
+          <t xml:space="preserve">  "g_text_audio": "가: 몇 시에 일어납니까?\n나: 여섯 시에 일어납니다.",</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "3": "남자가 아침에 운동을 하고 있다. 공원에서 조깅.",</t>
+          <t xml:space="preserve">  "content": [{</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "4": "남자가 아침 식사를 하고 있다. 식탁에 앉아 있다."</t>
+          <t xml:space="preserve">    "q_image_description": {</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">      "1": "남자가 아침 6시에 침대에서 일어나고 있다. 알람시계가 6:00을 가리킨다.",</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_answer": ["①", "②", "③", "④"],</t>
+          <t xml:space="preserve">      "2": "남자가 밤에 침대에 누워 자고 있다. 시계가 10:00을 가리킨다.",</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "q_correct": 1</t>
+          <t xml:space="preserve">      "3": "남자가 아침에 운동을 하고 있다. 공원에서 조깅.",</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }]</t>
+          <t xml:space="preserve">      "4": "남자가 아침 식사를 하고 있다. 식탁에 앉아 있다."</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_answer": ["①", "②", "③", "④"],</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "q_correct": 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
           <t>}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="37">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A42:F42"/>
@@ -5925,13 +6098,12 @@
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A48:F48"/>
@@ -5943,7 +6115,6 @@
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
